--- a/GPS-Speedsurfing-Board-Stats.xlsx
+++ b/GPS-Speedsurfing-Board-Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C79CE99-56ED-4831-9D35-25B49B369D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F90BB95-3121-45E4-B5B3-915AFF683F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,13 +757,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1067,808 +1065,823 @@
     <col min="11" max="11" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="E1" s="5" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="B3">
-        <v>6821</v>
+        <v>4845</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($E$1,B3),D3)</f>
-        <v>Custom Aurelio Verdi</v>
+        <v>X-Fire Ltd V3 122</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="B4">
-        <v>7087</v>
+        <v>4868</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="G4">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1" t="str">
-        <f t="shared" ref="K4:K67" si="0">HYPERLINK(_xlfn.CONCAT($E$1,B4),D4)</f>
-        <v>Custom Aurelio Verdi</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B4),D4)</f>
+        <v>X-Fire LTD V4</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="B5">
-        <v>7217</v>
+        <v>4869</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>192</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="G5">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>121</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Custom Aurelio Verdi</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B5),D5)</f>
+        <v>X-Fire LTD V4 90</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="B6">
-        <v>10820</v>
+        <v>4870</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>188</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="G6">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6">
+        <v>431</v>
+      </c>
+      <c r="J6">
         <v>22</v>
       </c>
-      <c r="I6">
-        <v>83</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
       <c r="K6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Fire Storm Wood V2</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B6),D6)</f>
+        <v>X-Fire LTD V4 114</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="B7">
-        <v>5783</v>
+        <v>4888</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I7">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove Ltd V2 102</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B7),D7)</f>
+        <v>X-FIRE V3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="B8">
-        <v>5784</v>
+        <v>4921</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="G8">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove Ltd V2 112</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B8),D8)</f>
+        <v>Firemove LTD</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B9">
-        <v>5785</v>
+        <v>4927</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>282</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove Ltd V2 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B9),D9)</f>
+        <v>X-Fire LTD V4 98</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B10">
-        <v>5786</v>
+        <v>4936</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="G10">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I10">
+        <v>83</v>
+      </c>
+      <c r="J10">
         <v>4</v>
       </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
       <c r="K10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove Ltd V2 130</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B10),D10)</f>
+        <v>Firemove LTD 100</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="B11">
-        <v>5787</v>
+        <v>4944</v>
       </c>
       <c r="C11" t="s">
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G11">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I11">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove Ltd V2 140</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B11),D11)</f>
+        <v>Fire Storm 111</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="B12">
-        <v>13559</v>
+        <v>4946</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="G12">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove V2 Wood</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B12),D12)</f>
+        <v>X-Fire LTD V4 129</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
+        <v>97</v>
+      </c>
+      <c r="B13">
+        <v>4954</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13">
+        <v>2012</v>
+      </c>
+      <c r="H13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13">
+        <v>373</v>
+      </c>
+      <c r="J13">
         <v>11</v>
       </c>
-      <c r="B13">
-        <v>9793</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13">
-        <v>2014</v>
-      </c>
-      <c r="H13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
       <c r="K13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>firestorm 111</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B13),D13)</f>
+        <v>X-Fire LTD V4 122</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="B14">
-        <v>7194</v>
+        <v>4965</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="G14">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I14">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firestorm LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B14),D14)</f>
+        <v>FireMove 110 X-Tech</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="B15">
-        <v>10003</v>
+        <v>4977</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="G15">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I15">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firestorm LTD V2</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B15),D15)</f>
+        <v>wave cult</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B16">
-        <v>10368</v>
+        <v>5010</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="G16">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I16">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firewave LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B16),D16)</f>
+        <v>X-Fire V4</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B17">
-        <v>9692</v>
+        <v>5012</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="G17">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
       </c>
       <c r="K17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>freerace</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B17),D17)</f>
+        <v>X-Fire LTD V4 105</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="B18">
-        <v>8251</v>
+        <v>5018</v>
       </c>
       <c r="C18" t="s">
         <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="G18">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
       </c>
       <c r="K18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>proto Firestorm V3 #053</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B18),D18)</f>
+        <v>FreestyleWave</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="B19">
-        <v>8266</v>
+        <v>5031</v>
       </c>
       <c r="C19" t="s">
         <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="G19">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>159</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Proto X-Fire 98 V7</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B19),D19)</f>
+        <v>Firemove LTD</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="B20">
-        <v>10170</v>
+        <v>5032</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="G20">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I20">
-        <v>5</v>
+        <v>130</v>
+      </c>
+      <c r="J20">
+        <v>6</v>
       </c>
       <c r="K20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Slalom</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B20),D20)</f>
+        <v>Firemove LTD 110</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B21">
-        <v>10287</v>
+        <v>5163</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="G21">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="I21">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
       </c>
       <c r="K21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Slalom Large Proto</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B21),D21)</f>
+        <v>X-Fire 80 V</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B22">
-        <v>5797</v>
+        <v>5191</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="G22">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I22">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="J22">
         <v>2</v>
       </c>
       <c r="K22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Speed 41</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B22),D22)</f>
+        <v>Firemove LTD</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="B23">
-        <v>9443</v>
+        <v>5196</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="G23">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I23">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>3</v>
       </c>
       <c r="K23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Speed 43</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B23),D23)</f>
+        <v>TwinTip LTD</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="B24">
-        <v>6951</v>
+        <v>5201</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="G24">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H24" t="s">
         <v>14</v>
@@ -1877,25 +1890,25 @@
         <v>9</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>speed board</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B24),D24)</f>
+        <v>Custom Speed</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B25">
-        <v>7238</v>
+        <v>5266</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E25" t="s">
         <v>51</v>
@@ -1904,1180 +1917,1189 @@
         <v>60</v>
       </c>
       <c r="G25">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H25" t="s">
         <v>58</v>
       </c>
       <c r="I25">
-        <v>23</v>
+        <v>589</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>x fire</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B25),D25)</f>
+        <v>X-Fire LTD V5 98</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B26">
-        <v>5753</v>
+        <v>5311</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G26">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I26">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="J26">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B26),D26)</f>
+        <v>X-Fire LTD V5 90</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B27">
-        <v>5703</v>
+        <v>5312</v>
       </c>
       <c r="C27" t="s">
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G27">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H27" t="s">
         <v>58</v>
       </c>
       <c r="I27">
-        <v>840</v>
+        <v>309</v>
       </c>
       <c r="J27">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 114</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B27),D27)</f>
+        <v>X-Fire LTD V5 105</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B28">
-        <v>5796</v>
+        <v>5313</v>
       </c>
       <c r="C28" t="s">
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="G28">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I28">
-        <v>134</v>
+        <v>417</v>
       </c>
       <c r="J28">
         <v>15</v>
       </c>
       <c r="K28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B28),D28)</f>
+        <v>X-Fire LTD V5 114</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B29">
-        <v>5702</v>
+        <v>5314</v>
       </c>
       <c r="C29" t="s">
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G29">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29">
+        <v>242</v>
+      </c>
+      <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B29),D29)</f>
+        <v>X-Fire LTD V5 122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>64</v>
       </c>
-      <c r="J29">
-        <v>5</v>
-      </c>
-      <c r="K29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <v>28</v>
-      </c>
-      <c r="B30" s="8">
-        <v>5795</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G30" s="8">
-        <v>2014</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="8">
-        <v>326</v>
-      </c>
-      <c r="J30" s="8">
-        <v>13</v>
+      <c r="B30">
+        <v>5315</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>144</v>
+      </c>
+      <c r="E30" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>2013</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30">
+        <v>214</v>
+      </c>
+      <c r="J30">
+        <v>14</v>
       </c>
       <c r="K30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 90</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B30),D30)</f>
+        <v>X-Fire LTD V5 129</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="B31">
-        <v>5738</v>
+        <v>5327</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="G31">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I31">
-        <v>479</v>
+        <v>13</v>
       </c>
       <c r="J31">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V6 98</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B31),D31)</f>
+        <v>Fire Strom LTD</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B32">
-        <v>7059</v>
+        <v>5397</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="E32" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G32">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H32" t="s">
         <v>58</v>
       </c>
       <c r="I32">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B32),D32)</f>
+        <v>X-Fire LTD V5 114 2013</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="B33">
-        <v>7060</v>
+        <v>5398</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="G33">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I33">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 114</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B33),D33)</f>
+        <v>Firemove 120</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B34">
-        <v>7061</v>
+        <v>5412</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>162</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
       </c>
       <c r="G34">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
       </c>
       <c r="I34">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B34),D34)</f>
+        <v>Firerace V3 122</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B35">
-        <v>7062</v>
+        <v>5425</v>
       </c>
       <c r="C35" t="s">
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G35">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 129</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B35),D35)</f>
+        <v>Firerace W-tech 102</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B36">
-        <v>7056</v>
+        <v>5426</v>
       </c>
       <c r="C36" t="s">
         <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="E36" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F36" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="G36">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="I36">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 80</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B36),D36)</f>
+        <v>Firerace W-tech 112</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>7057</v>
+        <v>5492</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="G37">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H37" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I37">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 90</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B37),D37)</f>
+        <v>Freestyle Wave</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B38">
-        <v>7058</v>
+        <v>5553</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G38">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H38" t="s">
         <v>58</v>
       </c>
       <c r="I38">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V7 98</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B38),D38)</f>
+        <v>FireMove 120 LTD</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>43</v>
+      </c>
+      <c r="B39">
+        <v>5554</v>
+      </c>
+      <c r="C39" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" t="s">
         <v>37</v>
       </c>
-      <c r="B39">
-        <v>14103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" t="s">
-        <v>100</v>
-      </c>
-      <c r="E39" t="s">
-        <v>86</v>
-      </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G39">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
       <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39">
         <v>2</v>
       </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
       <c r="K39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire V5 LTD 128</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B39),D39)</f>
+        <v>FireMove 140 LTD</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B40">
-        <v>5678</v>
+        <v>5555</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="G40">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I40">
-        <v>75</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>XiFire LTD V6 90</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B40),D40)</f>
+        <v>FireWave 102 LTD</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B41">
-        <v>5581</v>
+        <v>5576</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="F41" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="G41">
         <v>2013</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="I41">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Custom Speed</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B41),D41)</f>
+        <v>Firestorm 120 W-tech</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42">
-        <v>9415</v>
+        <v>5581</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F42" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="G42">
         <v>2013</v>
       </c>
       <c r="H42" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I42">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B42),D42)</f>
+        <v>Custom Speed</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B43">
-        <v>14364</v>
+        <v>5664</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E43" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="G43">
         <v>2013</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
       </c>
       <c r="K43" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>firemove</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B43),D43)</f>
+        <v>firerace</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B44">
-        <v>5553</v>
+        <v>5678</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E44" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="G44">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="J44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>FireMove 120 LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B44),D44)</f>
+        <v>XiFire LTD V6 90</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>5554</v>
+        <v>5702</v>
       </c>
       <c r="C45" t="s">
         <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G45">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K45" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>FireMove 140 LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B45),D45)</f>
+        <v>X-Fire LTD V6 129</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B46">
-        <v>9928</v>
+        <v>5703</v>
       </c>
       <c r="C46" t="s">
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="G46">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I46">
-        <v>7</v>
+        <v>840</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K46" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B46),D46)</f>
+        <v>X-Fire LTD V6 114</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B47">
-        <v>5191</v>
+        <v>5738</v>
       </c>
       <c r="C47" t="s">
         <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="F47" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="G47">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H47" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="I47">
-        <v>62</v>
+        <v>479</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K47" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B47),D47)</f>
+        <v>X-Fire LTD V6 98</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B48">
-        <v>10208</v>
+        <v>5753</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F48" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="G48">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I48">
-        <v>11</v>
+        <v>612</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="K48" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firemove LTD 130</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B48),D48)</f>
+        <v>X-Fire LTD V6 105</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B49">
-        <v>5664</v>
+        <v>5783</v>
       </c>
       <c r="C49" t="s">
         <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="E49" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F49" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G49">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H49" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>firerace</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B49),D49)</f>
+        <v>Firemove Ltd V2 102</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B50">
-        <v>5425</v>
+        <v>5784</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F50" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G50">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I50">
+        <v>13</v>
+      </c>
+      <c r="J50">
         <v>4</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firerace W-tech 102</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B50),D50)</f>
+        <v>Firemove Ltd V2 112</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="B51">
-        <v>5426</v>
+        <v>5785</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G51">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H51" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firerace W-tech 112</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B51),D51)</f>
+        <v>Firemove Ltd V2 122</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B52">
-        <v>5576</v>
+        <v>5786</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>33</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F52" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G52">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I52">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Firestorm 120 W-tech</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B52),D52)</f>
+        <v>Firemove Ltd V2 130</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B53">
-        <v>5555</v>
+        <v>5787</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="E53" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G53">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H53" t="s">
         <v>26</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
       </c>
       <c r="K53" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>FireWave 102 LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B53),D53)</f>
+        <v>Firemove Ltd V2 140</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54">
-        <v>5492</v>
-      </c>
-      <c r="C54" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54" t="s">
-        <v>128</v>
-      </c>
-      <c r="G54">
-        <v>2013</v>
-      </c>
-      <c r="H54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I54">
-        <v>29</v>
-      </c>
-      <c r="J54">
-        <v>1</v>
+      <c r="A54" s="6">
+        <v>28</v>
+      </c>
+      <c r="B54" s="6">
+        <v>5795</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G54" s="6">
+        <v>2014</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="6">
+        <v>326</v>
+      </c>
+      <c r="J54" s="6">
+        <v>13</v>
       </c>
       <c r="K54" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Freestyle Wave</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B54),D54)</f>
+        <v>X-Fire LTD V6 90</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B55">
-        <v>6930</v>
+        <v>5796</v>
       </c>
       <c r="C55" t="s">
         <v>10</v>
       </c>
       <c r="D55" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="F55" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="G55">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H55" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I55">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K55" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Freestyle Wave LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B55),D55)</f>
+        <v>X-Fire LTD V6 122</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B56">
-        <v>10156</v>
+        <v>5797</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="E56" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="F56" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="G56">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I56">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Freestyle Wave LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B56),D56)</f>
+        <v>Speed 41</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="B57">
-        <v>10490</v>
+        <v>6821</v>
       </c>
       <c r="C57" t="s">
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G57">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H57" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
       </c>
       <c r="K57" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>FreeStyleWave</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B57),D57)</f>
+        <v>Custom Aurelio Verdi</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B58">
-        <v>10476</v>
+        <v>6930</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E58" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="G58">
         <v>2013</v>
@@ -3086,772 +3108,766 @@
         <v>26</v>
       </c>
       <c r="I58">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K58" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Frrestyle Wave 102</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B58),D58)</f>
+        <v>Freestyle Wave LTD</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B59">
-        <v>14962</v>
+        <v>6940</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="G59">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H59" t="s">
         <v>58</v>
       </c>
+      <c r="I59">
+        <v>23</v>
+      </c>
+      <c r="J59">
+        <v>3</v>
+      </c>
       <c r="K59" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Slalom</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B59),D59)</f>
+        <v>Fire Storm 138 W-Tech</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="B60">
-        <v>10426</v>
+        <v>6951</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E60" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="F60" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G60">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H60" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="I60">
+        <v>9</v>
+      </c>
+      <c r="J60">
         <v>1</v>
       </c>
-      <c r="J60">
-        <v>2</v>
-      </c>
       <c r="K60" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Slalom/speed</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B60),D60)</f>
+        <v>speed board</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B61">
-        <v>10110</v>
+        <v>7038</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="E61" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="F61" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="G61">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H61" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I61">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K61" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-fire LTD V5</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B61),D61)</f>
+        <v>Firestorm</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B62">
-        <v>5312</v>
+        <v>7056</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="E62" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="F62" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G62">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I62">
-        <v>309</v>
+        <v>31</v>
       </c>
       <c r="J62">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B62),D62)</f>
+        <v>X-Fire LTD V7 80</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
+        <v>35</v>
+      </c>
+      <c r="B63">
+        <v>7057</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>98</v>
+      </c>
+      <c r="E63" t="s">
+        <v>88</v>
+      </c>
+      <c r="F63" t="s">
+        <v>89</v>
+      </c>
+      <c r="G63">
+        <v>2014</v>
+      </c>
+      <c r="H63" t="s">
         <v>61</v>
       </c>
-      <c r="B63">
-        <v>5313</v>
-      </c>
-      <c r="C63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" t="s">
-        <v>141</v>
-      </c>
-      <c r="E63" t="s">
-        <v>81</v>
-      </c>
-      <c r="F63" t="s">
-        <v>82</v>
-      </c>
-      <c r="G63">
-        <v>2013</v>
-      </c>
-      <c r="H63" t="s">
-        <v>58</v>
-      </c>
       <c r="I63">
-        <v>417</v>
+        <v>42</v>
       </c>
       <c r="J63">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K63" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 114</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B63),D63)</f>
+        <v>X-Fire LTD V7 90</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B64">
-        <v>5397</v>
+        <v>7058</v>
       </c>
       <c r="C64" t="s">
         <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E64" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="F64" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="G64">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H64" t="s">
         <v>58</v>
       </c>
       <c r="I64">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J64">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K64" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 114 2013</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B64),D64)</f>
+        <v>X-Fire LTD V7 98</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B65">
-        <v>5314</v>
+        <v>7059</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="E65" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="G65">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I65">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="J65">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K65" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B65),D65)</f>
+        <v>X-Fire LTD V7 105</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B66">
-        <v>5315</v>
+        <v>7060</v>
       </c>
       <c r="C66" t="s">
         <v>10</v>
       </c>
       <c r="D66" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="E66" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="G66">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H66" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I66">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="J66">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K66" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 129</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B66),D66)</f>
+        <v>X-Fire LTD V7 114</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B67">
-        <v>5311</v>
+        <v>7061</v>
       </c>
       <c r="C67" t="s">
         <v>10</v>
       </c>
       <c r="D67" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="F67" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="G67">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H67" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="I67">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K67" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>X-Fire LTD V5 90</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B67),D67)</f>
+        <v>X-Fire LTD V7 122</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B68">
-        <v>5266</v>
+        <v>7062</v>
       </c>
       <c r="C68" t="s">
         <v>10</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F68" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="G68">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I68">
-        <v>589</v>
+        <v>7</v>
       </c>
       <c r="J68">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K68" s="1" t="str">
-        <f t="shared" ref="K68:K104" si="1">HYPERLINK(_xlfn.CONCAT($E$1,B68),D68)</f>
-        <v>X-Fire LTD V5 98</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B68),D68)</f>
+        <v>X-Fire LTD V7 129</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B69">
-        <v>5201</v>
+        <v>7087</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
       </c>
       <c r="D69" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G69">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H69" t="s">
         <v>14</v>
       </c>
       <c r="I69">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Custom Speed</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B69),D69)</f>
+        <v>Custom Aurelio Verdi</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B70">
-        <v>4944</v>
+        <v>7194</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="F70" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G70">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I70">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Fire Storm 111</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B70),D70)</f>
+        <v>Firestorm LTD</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B71">
-        <v>6940</v>
+        <v>7217</v>
       </c>
       <c r="C71" t="s">
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>149</v>
+        <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G71">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="I71">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Fire Storm 138 W-Tech</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B71),D71)</f>
+        <v>Custom Aurelio Verdi</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="B72">
-        <v>5327</v>
+        <v>7238</v>
       </c>
       <c r="C72" t="s">
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E72" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F72" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G72">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H72" t="s">
         <v>58</v>
       </c>
       <c r="I72">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Fire Strom LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B72),D72)</f>
+        <v>x fire</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="B73">
-        <v>14552</v>
+        <v>8251</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="E73" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="F73" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="G73">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H73" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="I73">
-        <v>6</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K73" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>firemove 100</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B73),D73)</f>
+        <v>proto Firestorm V3 #053</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="B74">
-        <v>13922</v>
+        <v>8266</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="F74" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="G74">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I74">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>FireMove 100 X-Tech</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B74),D74)</f>
+        <v>Proto X-Fire 98 V7</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B75">
-        <v>14551</v>
+        <v>9415</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
       </c>
       <c r="D75" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="F75" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="G75">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H75" t="s">
         <v>26</v>
       </c>
       <c r="I75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J75">
         <v>1</v>
       </c>
       <c r="K75" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>firemove 110</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B75),D75)</f>
+        <v>Firemove</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="B76">
-        <v>4965</v>
+        <v>9443</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="E76" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="F76" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="G76">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H76" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K76" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>FireMove 110 X-Tech</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B76),D76)</f>
+        <v>Speed 43</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B77">
-        <v>5398</v>
+        <v>9639</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="E77" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G77">
         <v>2012</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="I77">
-        <v>25</v>
-      </c>
-      <c r="J77">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K77" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firemove 120</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B77),D77)</f>
+        <v>X-Fire LTD 105</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="B78">
-        <v>14541</v>
+        <v>9692</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="E78" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="F78" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="G78">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H78" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="I78">
         <v>1</v>
       </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
       <c r="K78" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firemove LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B78),D78)</f>
+        <v>freerace</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="B79">
-        <v>5031</v>
+        <v>9793</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
       </c>
       <c r="D79" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="E79" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="F79" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="G79">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H79" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="I79">
-        <v>31</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firemove LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B79),D79)</f>
+        <v>firestorm 111</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B80">
-        <v>4921</v>
+        <v>9928</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
@@ -3860,190 +3876,187 @@
         <v>115</v>
       </c>
       <c r="E80" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="F80" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="G80">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H80" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I80">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K80" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B80),D80)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="B81">
-        <v>4936</v>
+        <v>10003</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="E81" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="F81" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="G81">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H81" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I81">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firemove LTD 100</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B81),D81)</f>
+        <v>Firestorm LTD V2</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B82">
-        <v>5032</v>
+        <v>10110</v>
       </c>
       <c r="C82" t="s">
         <v>10</v>
       </c>
       <c r="D82" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="E82" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F82" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="G82">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I82">
-        <v>130</v>
+        <v>6</v>
       </c>
       <c r="J82">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K82" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firemove LTD 110</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B82),D82)</f>
+        <v>X-fire LTD V5</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="B83">
-        <v>5412</v>
+        <v>10156</v>
       </c>
       <c r="C83" t="s">
         <v>10</v>
       </c>
       <c r="D83" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="E83" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="G83">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J83">
         <v>1</v>
       </c>
       <c r="K83" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firerace V3 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B83),D83)</f>
+        <v>Freestyle Wave LTD</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="B84">
-        <v>7038</v>
+        <v>10170</v>
       </c>
       <c r="C84" t="s">
         <v>10</v>
       </c>
       <c r="D84" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="E84" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="F84" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G84">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="I84">
-        <v>73</v>
-      </c>
-      <c r="J84">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K84" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Firestorm</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B84),D84)</f>
+        <v>Slalom</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B85">
-        <v>12125</v>
+        <v>10193</v>
       </c>
       <c r="C85" t="s">
         <v>10</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="E85" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="F85" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G85">
         <v>2012</v>
@@ -4052,670 +4065,661 @@
         <v>26</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J85">
         <v>1</v>
       </c>
       <c r="K85" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Freestyle Wave</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B85),D85)</f>
+        <v>Freestyle Wave 96 LTD</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="B86">
-        <v>14198</v>
+        <v>10208</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="E86" t="s">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="F86" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="G86">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H86" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I86">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J86">
         <v>1</v>
       </c>
       <c r="K86" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Freestyle Wave 90 X-Tech</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B86),D86)</f>
+        <v>Firemove LTD 130</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="B87">
-        <v>10193</v>
+        <v>10287</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="F87" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="G87">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H87" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="I87">
-        <v>33</v>
-      </c>
-      <c r="J87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K87" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>Freestyle Wave 96 LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B87),D87)</f>
+        <v>Slalom Large Proto</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="B88">
-        <v>5018</v>
+        <v>10368</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
       </c>
       <c r="D88" t="s">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="E88" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="F88" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="G88">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H88" t="s">
         <v>26</v>
       </c>
       <c r="I88">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="J88">
         <v>1</v>
       </c>
       <c r="K88" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>FreestyleWave</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B88),D88)</f>
+        <v>Firewave LTD</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="B89">
-        <v>5196</v>
+        <v>10426</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
       </c>
       <c r="D89" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="E89" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="F89" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="G89">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H89" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="I89">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>TwinTip LTD</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B89),D89)</f>
+        <v>Slalom/speed</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B90">
-        <v>4977</v>
+        <v>10476</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="E90" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="F90" t="s">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="G90">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H90" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K90" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>wave cult</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B90),D90)</f>
+        <v>Frrestyle Wave 102</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="B91">
-        <v>15015</v>
+        <v>10490</v>
       </c>
       <c r="C91" t="s">
         <v>10</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="E91" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="F91" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="G91">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>26</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
       </c>
       <c r="K91" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-fire</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B91),D91)</f>
+        <v>FreeStyleWave</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="B92">
-        <v>14981</v>
+        <v>10820</v>
       </c>
       <c r="C92" t="s">
         <v>10</v>
       </c>
       <c r="D92" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="F92" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="G92">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H92" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="I92">
+        <v>83</v>
+      </c>
+      <c r="J92">
         <v>1</v>
       </c>
       <c r="K92" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>xfire 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B92),D92)</f>
+        <v>Fire Storm Wood V2</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B93">
-        <v>5163</v>
+        <v>12125</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="E93" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="F93" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="G93">
         <v>2012</v>
       </c>
       <c r="H93" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="I93">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K93" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire 80 V</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B93),D93)</f>
+        <v>Freestyle Wave</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="B94">
-        <v>9639</v>
+        <v>13559</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>183</v>
+        <v>39</v>
       </c>
       <c r="E94" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="G94">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I94">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
       </c>
       <c r="K94" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B94),D94)</f>
+        <v>Firemove V2 Wood</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B95">
-        <v>4845</v>
+        <v>13922</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
       </c>
       <c r="D95" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="E95" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="G95">
         <v>2012</v>
       </c>
       <c r="H95" t="s">
+        <v>58</v>
+      </c>
+      <c r="I95">
         <v>22</v>
       </c>
-      <c r="I95">
-        <v>45</v>
-      </c>
       <c r="J95">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K95" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire Ltd V3 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B95),D95)</f>
+        <v>FireMove 100 X-Tech</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="B96">
-        <v>4868</v>
+        <v>14103</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
       </c>
       <c r="D96" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="G96">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I96">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K96" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B96),D96)</f>
+        <v>X-Fire V5 LTD 128</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B97">
-        <v>5012</v>
+        <v>14198</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E97" t="s">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="F97" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G97">
         <v>2012</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="I97">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K97" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 105</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B97),D97)</f>
+        <v>Freestyle Wave 90 X-Tech</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="B98">
-        <v>4870</v>
+        <v>14364</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
       </c>
       <c r="D98" t="s">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="E98" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="F98" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="G98">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H98" t="s">
         <v>58</v>
       </c>
-      <c r="I98">
-        <v>431</v>
-      </c>
-      <c r="J98">
-        <v>22</v>
-      </c>
       <c r="K98" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 114</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B98),D98)</f>
+        <v>firemove</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B99">
-        <v>4954</v>
+        <v>14541</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
       </c>
       <c r="D99" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="E99" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="G99">
         <v>2012</v>
       </c>
       <c r="H99" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
       <c r="I99">
-        <v>373</v>
+        <v>1</v>
       </c>
       <c r="J99">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K99" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 122</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B99),D99)</f>
+        <v>Firemove LTD</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B100">
-        <v>4946</v>
+        <v>14551</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="E100" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
       <c r="F100" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="G100">
         <v>2012</v>
       </c>
       <c r="H100" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="I100">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="J100">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K100" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 129</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B100),D100)</f>
+        <v>firemove 110</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B101">
-        <v>4869</v>
+        <v>14552</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
       </c>
       <c r="D101" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="E101" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="F101" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="G101">
         <v>2012</v>
       </c>
       <c r="H101" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="I101">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="J101">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K101" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 90</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B101),D101)</f>
+        <v>firemove 100</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="B102">
-        <v>4927</v>
+        <v>14962</v>
       </c>
       <c r="C102" t="s">
         <v>10</v>
       </c>
       <c r="D102" t="s">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="E102" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="F102" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="G102">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H102" t="s">
         <v>58</v>
       </c>
-      <c r="I102">
-        <v>282</v>
-      </c>
-      <c r="J102">
-        <v>15</v>
-      </c>
       <c r="K102" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire LTD V4 98</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B102),D102)</f>
+        <v>Slalom</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B103">
-        <v>4888</v>
+        <v>14981</v>
       </c>
       <c r="C103" t="s">
         <v>10</v>
       </c>
       <c r="D103" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="E103" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F103" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="G103">
         <v>2012</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I103">
-        <v>106</v>
-      </c>
-      <c r="J103">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K103" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-FIRE V3</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B103),D103)</f>
+        <v>xfire 105</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B104">
-        <v>5010</v>
+        <v>15015</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="E104" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="F104" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="G104">
         <v>2012</v>
@@ -4723,19 +4727,17 @@
       <c r="H104" t="s">
         <v>58</v>
       </c>
-      <c r="I104">
-        <v>6</v>
-      </c>
-      <c r="J104">
-        <v>1</v>
-      </c>
       <c r="K104" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>X-Fire V4</v>
+        <f>HYPERLINK(_xlfn.CONCAT($E$1,B104),D104)</f>
+        <v>X-fire</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}"/>
+  <autoFilter ref="A2:K2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:K104">
+      <sortCondition ref="B2"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4746,16 +4748,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="10">
+      <c r="A1" s="8">
         <v>2013</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
         <v>198</v>
       </c>
       <c r="I1" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" t="s">
         <v>196</v>
       </c>
     </row>

--- a/GPS-Speedsurfing-Board-Stats.xlsx
+++ b/GPS-Speedsurfing-Board-Stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AD3CB9-EE90-4716-8DFC-CDB1D729877F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFCAE7-DFED-4F4F-9EA4-C5B23D88239C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Board Stats" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="379">
   <si>
     <t>#</t>
   </si>
@@ -1008,6 +1008,177 @@
   </si>
   <si>
     <t>Dublett Berra</t>
+  </si>
+  <si>
+    <t>AllWave</t>
+  </si>
+  <si>
+    <t>85 l</t>
+  </si>
+  <si>
+    <t>Eagle</t>
+  </si>
+  <si>
+    <t>126 l</t>
+  </si>
+  <si>
+    <t>Eagle 100</t>
+  </si>
+  <si>
+    <t>63 x 245 cm</t>
+  </si>
+  <si>
+    <t>Eagle 126</t>
+  </si>
+  <si>
+    <t>69 x 249 cm</t>
+  </si>
+  <si>
+    <t>Falcon</t>
+  </si>
+  <si>
+    <t>61 x 245 cm</t>
+  </si>
+  <si>
+    <t>Falcon 105</t>
+  </si>
+  <si>
+    <t>67 x 245 cm</t>
+  </si>
+  <si>
+    <t>Falcon 125</t>
+  </si>
+  <si>
+    <t>76 x 245 cm</t>
+  </si>
+  <si>
+    <t>125 l</t>
+  </si>
+  <si>
+    <t>Falcon 145</t>
+  </si>
+  <si>
+    <t>85 x 245 cm</t>
+  </si>
+  <si>
+    <t>145 l</t>
+  </si>
+  <si>
+    <t>Falcon 90</t>
+  </si>
+  <si>
+    <t>Falcon 90 Proto</t>
+  </si>
+  <si>
+    <t>Falcon Formula TT</t>
+  </si>
+  <si>
+    <t>100 x 250 cm</t>
+  </si>
+  <si>
+    <t>155 l</t>
+  </si>
+  <si>
+    <t>Falcon prototype</t>
+  </si>
+  <si>
+    <t>70 x 245 cm</t>
+  </si>
+  <si>
+    <t>132 l</t>
+  </si>
+  <si>
+    <t>Falcon SL 105</t>
+  </si>
+  <si>
+    <t>Falcon SL 145</t>
+  </si>
+  <si>
+    <t>Falcon SL90</t>
+  </si>
+  <si>
+    <t>Falcon Slalom 105</t>
+  </si>
+  <si>
+    <t>68 x 245 cm</t>
+  </si>
+  <si>
+    <t>Falcon Speed</t>
+  </si>
+  <si>
+    <t>69 l</t>
+  </si>
+  <si>
+    <t>Freemove</t>
+  </si>
+  <si>
+    <t>59 x 243 cm</t>
+  </si>
+  <si>
+    <t>95 l</t>
+  </si>
+  <si>
+    <t>Freewave</t>
+  </si>
+  <si>
+    <t>56 x 236 cm</t>
+  </si>
+  <si>
+    <t>Freewave 104</t>
+  </si>
+  <si>
+    <t>64 x 241 cm</t>
+  </si>
+  <si>
+    <t>Freewave 86</t>
+  </si>
+  <si>
+    <t>58 x 239 cm</t>
+  </si>
+  <si>
+    <t>86 l</t>
+  </si>
+  <si>
+    <t>Freewave 95</t>
+  </si>
+  <si>
+    <t>61 x 241 cm</t>
+  </si>
+  <si>
+    <t>Hawk 108</t>
+  </si>
+  <si>
+    <t>62 x 247 cm</t>
+  </si>
+  <si>
+    <t>108 l</t>
+  </si>
+  <si>
+    <t>Hawk 123</t>
+  </si>
+  <si>
+    <t>66 x 249 cm</t>
+  </si>
+  <si>
+    <t>123 l</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>75 x 260 cm</t>
+  </si>
+  <si>
+    <t>Shark 130 Ltd</t>
+  </si>
+  <si>
+    <t>70 x 258 cm</t>
+  </si>
+  <si>
+    <t>Shark HRS 145 L</t>
+  </si>
+  <si>
+    <t>75 x 263 cm</t>
   </si>
 </sst>
 </file>
@@ -1504,27 +1675,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
-  <dimension ref="A1:M154"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M181"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" style="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.140625" customWidth="1"/>
-    <col min="13" max="13" width="26.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.109375" customWidth="1"/>
+    <col min="13" max="13" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="F1" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>318</v>
       </c>
@@ -1565,7 +1736,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -1601,7 +1772,7 @@
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -1637,7 +1808,7 @@
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1673,7 +1844,7 @@
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1709,7 +1880,7 @@
         <v>Fire Storm Wood V2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1745,7 +1916,7 @@
         <v>Firemove Ltd V2 102</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1781,7 +1952,7 @@
         <v>Firemove Ltd V2 112</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1817,7 +1988,7 @@
         <v>Firemove Ltd V2 122</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1853,7 +2024,7 @@
         <v>Firemove Ltd V2 130</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1889,7 +2060,7 @@
         <v>Firemove Ltd V2 140</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -1925,7 +2096,7 @@
         <v>Firemove V2 Wood</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>11</v>
       </c>
@@ -1958,7 +2129,7 @@
         <v>firestorm 111</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>12</v>
       </c>
@@ -1994,7 +2165,7 @@
         <v>Firestorm LTD</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>13</v>
       </c>
@@ -2030,7 +2201,7 @@
         <v>Firestorm LTD V2</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>14</v>
       </c>
@@ -2066,7 +2237,7 @@
         <v>Firewave LTD</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -2099,7 +2270,7 @@
         <v>freerace</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>16</v>
       </c>
@@ -2132,7 +2303,7 @@
         <v>proto Firestorm V3 #053</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>17</v>
       </c>
@@ -2168,7 +2339,7 @@
         <v>Proto X-Fire 98 V7</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>18</v>
       </c>
@@ -2201,7 +2372,7 @@
         <v>Slalom</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>19</v>
       </c>
@@ -2234,7 +2405,7 @@
         <v>Slalom Large Proto</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20</v>
       </c>
@@ -2270,7 +2441,7 @@
         <v>Speed 41</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>21</v>
       </c>
@@ -2306,7 +2477,7 @@
         <v>Speed 43</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>22</v>
       </c>
@@ -2342,7 +2513,7 @@
         <v>speed board</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>23</v>
       </c>
@@ -2378,7 +2549,7 @@
         <v>x fire</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>24</v>
       </c>
@@ -2414,7 +2585,7 @@
         <v>X-Fire LTD V6 105</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>25</v>
       </c>
@@ -2450,7 +2621,7 @@
         <v>X-Fire LTD V6 114</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>26</v>
       </c>
@@ -2486,7 +2657,7 @@
         <v>X-Fire LTD V6 122</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>27</v>
       </c>
@@ -2522,7 +2693,7 @@
         <v>X-Fire LTD V6 129</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>320</v>
       </c>
@@ -2562,7 +2733,7 @@
         <v>X-Fire LTD V6 90</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>29</v>
       </c>
@@ -2598,7 +2769,7 @@
         <v>X-Fire LTD V6 98</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>30</v>
       </c>
@@ -2634,7 +2805,7 @@
         <v>X-Fire LTD V7 105</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>31</v>
       </c>
@@ -2670,7 +2841,7 @@
         <v>X-Fire LTD V7 114</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>32</v>
       </c>
@@ -2706,7 +2877,7 @@
         <v>X-Fire LTD V7 122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>33</v>
       </c>
@@ -2742,7 +2913,7 @@
         <v>X-Fire LTD V7 129</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>34</v>
       </c>
@@ -2778,7 +2949,7 @@
         <v>X-Fire LTD V7 80</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>35</v>
       </c>
@@ -2814,7 +2985,7 @@
         <v>X-Fire LTD V7 90</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>36</v>
       </c>
@@ -2850,7 +3021,7 @@
         <v>X-Fire LTD V7 98</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>37</v>
       </c>
@@ -2886,7 +3057,7 @@
         <v>X-Fire V5 LTD 128</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>321</v>
       </c>
@@ -2926,7 +3097,7 @@
         <v>XiFire LTD V6 90</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>39</v>
       </c>
@@ -2962,7 +3133,7 @@
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>40</v>
       </c>
@@ -2998,7 +3169,7 @@
         <v>Firemove</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>41</v>
       </c>
@@ -3028,7 +3199,7 @@
         <v>firemove</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
       <c r="B44">
         <v>42</v>
@@ -3065,7 +3236,7 @@
         <v>FireMove 120 LTD</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>43</v>
       </c>
@@ -3101,7 +3272,7 @@
         <v>FireMove 140 LTD</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>44</v>
       </c>
@@ -3137,7 +3308,7 @@
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>45</v>
       </c>
@@ -3173,7 +3344,7 @@
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>46</v>
       </c>
@@ -3209,7 +3380,7 @@
         <v>Firemove LTD 130</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>47</v>
       </c>
@@ -3245,7 +3416,7 @@
         <v>firerace</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>48</v>
       </c>
@@ -3281,7 +3452,7 @@
         <v>Firerace W-tech 102</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>49</v>
       </c>
@@ -3317,7 +3488,7 @@
         <v>Firerace W-tech 112</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>50</v>
       </c>
@@ -3353,7 +3524,7 @@
         <v>Firestorm 120 W-tech</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>51</v>
       </c>
@@ -3386,7 +3557,7 @@
         <v>FireWave 102 LTD</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54">
         <v>52</v>
@@ -3423,7 +3594,7 @@
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>53</v>
       </c>
@@ -3459,7 +3630,7 @@
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>54</v>
       </c>
@@ -3495,7 +3666,7 @@
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>55</v>
       </c>
@@ -3528,7 +3699,7 @@
         <v>FreeStyleWave</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>56</v>
       </c>
@@ -3564,7 +3735,7 @@
         <v>Frrestyle Wave 102</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>57</v>
       </c>
@@ -3594,7 +3765,7 @@
         <v>Slalom</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>58</v>
       </c>
@@ -3630,7 +3801,7 @@
         <v>Slalom/speed</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>59</v>
       </c>
@@ -3666,7 +3837,7 @@
         <v>X-fire LTD V5</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>60</v>
       </c>
@@ -3702,7 +3873,7 @@
         <v>X-Fire LTD V5 105</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>61</v>
       </c>
@@ -3738,7 +3909,7 @@
         <v>X-Fire LTD V5 114</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>62</v>
       </c>
@@ -3774,7 +3945,7 @@
         <v>X-Fire LTD V5 114 2013</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>63</v>
       </c>
@@ -3810,7 +3981,7 @@
         <v>X-Fire LTD V5 122</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>64</v>
       </c>
@@ -3846,7 +4017,7 @@
         <v>X-Fire LTD V5 129</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>65</v>
       </c>
@@ -3882,7 +4053,7 @@
         <v>X-Fire LTD V5 90</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>66</v>
       </c>
@@ -3918,7 +4089,7 @@
         <v>X-Fire LTD V5 98</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>67</v>
       </c>
@@ -3954,7 +4125,7 @@
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>68</v>
       </c>
@@ -3990,7 +4161,7 @@
         <v>Fire Storm 111</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>69</v>
       </c>
@@ -4026,7 +4197,7 @@
         <v>Fire Storm 138 W-Tech</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>70</v>
       </c>
@@ -4062,7 +4233,7 @@
         <v>Fire Strom LTD</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>71</v>
       </c>
@@ -4098,7 +4269,7 @@
         <v>firemove 100</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>72</v>
       </c>
@@ -4134,7 +4305,7 @@
         <v>FireMove 100 X-Tech</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>73</v>
       </c>
@@ -4170,7 +4341,7 @@
         <v>firemove 110</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>74</v>
       </c>
@@ -4206,7 +4377,7 @@
         <v>FireMove 110 X-Tech</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>75</v>
       </c>
@@ -4242,7 +4413,7 @@
         <v>Firemove 120</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>76</v>
       </c>
@@ -4278,7 +4449,7 @@
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>77</v>
       </c>
@@ -4314,7 +4485,7 @@
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>78</v>
       </c>
@@ -4350,7 +4521,7 @@
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>79</v>
       </c>
@@ -4386,7 +4557,7 @@
         <v>Firemove LTD 100</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>80</v>
       </c>
@@ -4422,7 +4593,7 @@
         <v>Firemove LTD 110</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>81</v>
       </c>
@@ -4458,7 +4629,7 @@
         <v>Firerace V3 122</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>82</v>
       </c>
@@ -4494,7 +4665,7 @@
         <v>Firestorm</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>83</v>
       </c>
@@ -4530,7 +4701,7 @@
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>84</v>
       </c>
@@ -4566,7 +4737,7 @@
         <v>Freestyle Wave 90 X-Tech</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>85</v>
       </c>
@@ -4602,7 +4773,7 @@
         <v>Freestyle Wave 96 LTD</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>86</v>
       </c>
@@ -4638,7 +4809,7 @@
         <v>FreestyleWave</v>
       </c>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>87</v>
       </c>
@@ -4674,7 +4845,7 @@
         <v>TwinTip LTD</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>88</v>
       </c>
@@ -4710,7 +4881,7 @@
         <v>wave cult</v>
       </c>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>89</v>
       </c>
@@ -4740,7 +4911,7 @@
         <v>X-fire</v>
       </c>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>90</v>
       </c>
@@ -4773,7 +4944,7 @@
         <v>xfire 105</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>91</v>
       </c>
@@ -4809,7 +4980,7 @@
         <v>X-Fire 80 V</v>
       </c>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>92</v>
       </c>
@@ -4842,7 +5013,7 @@
         <v>X-Fire LTD 105</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>93</v>
       </c>
@@ -4878,7 +5049,7 @@
         <v>X-Fire Ltd V3 122</v>
       </c>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>94</v>
       </c>
@@ -4914,7 +5085,7 @@
         <v>X-Fire LTD V4</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>95</v>
       </c>
@@ -4950,7 +5121,7 @@
         <v>X-Fire LTD V4 105</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>96</v>
       </c>
@@ -4986,7 +5157,7 @@
         <v>X-Fire LTD V4 114</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>97</v>
       </c>
@@ -5022,7 +5193,7 @@
         <v>X-Fire LTD V4 122</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>98</v>
       </c>
@@ -5058,7 +5229,7 @@
         <v>X-Fire LTD V4 129</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>99</v>
       </c>
@@ -5094,7 +5265,7 @@
         <v>X-Fire LTD V4 90</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>100</v>
       </c>
@@ -5130,7 +5301,7 @@
         <v>X-Fire LTD V4 98</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>101</v>
       </c>
@@ -5166,7 +5337,7 @@
         <v>X-FIRE V3</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>102</v>
       </c>
@@ -5202,7 +5373,7 @@
         <v>X-Fire V4</v>
       </c>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>103</v>
       </c>
@@ -5238,7 +5409,7 @@
         <v>Atom IQ</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>104</v>
       </c>
@@ -5277,7 +5448,7 @@
         <v>Atom IQ 100 Tufskin</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>105</v>
       </c>
@@ -5316,7 +5487,7 @@
         <v>Atom IQ carbon 110</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>106</v>
       </c>
@@ -5355,7 +5526,7 @@
         <v>AtomIQ 120 Carbon</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>107</v>
       </c>
@@ -5394,7 +5565,7 @@
         <v>Carve 111 wood</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>108</v>
       </c>
@@ -5433,7 +5604,7 @@
         <v>Fórmula 167 blue</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>109</v>
       </c>
@@ -5472,7 +5643,7 @@
         <v>Futura</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>110</v>
       </c>
@@ -5511,7 +5682,7 @@
         <v>Futura 104 carbon</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>111</v>
       </c>
@@ -5550,7 +5721,7 @@
         <v>Futura 104 wood</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>112</v>
       </c>
@@ -5589,7 +5760,7 @@
         <v>Futura 114 carbon</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>113</v>
       </c>
@@ -5628,7 +5799,7 @@
         <v>Futura 114 wood</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>114</v>
       </c>
@@ -5667,7 +5838,7 @@
         <v>Futura 124 Carbon</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>115</v>
       </c>
@@ -5706,7 +5877,7 @@
         <v>Futura 124 Wood</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>116</v>
       </c>
@@ -5745,7 +5916,7 @@
         <v>Futura 133 Wood</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>117</v>
       </c>
@@ -5784,7 +5955,7 @@
         <v>Futura 134 Carbon</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>118</v>
       </c>
@@ -5823,7 +5994,7 @@
         <v>Futura 134 Wood</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>119</v>
       </c>
@@ -5862,7 +6033,7 @@
         <v>Futura 90 Wood</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>120</v>
       </c>
@@ -5901,7 +6072,7 @@
         <v>Futura 93 wood</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>121</v>
       </c>
@@ -5940,7 +6111,7 @@
         <v>Futura 97 wood</v>
       </c>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>122</v>
       </c>
@@ -5979,7 +6150,7 @@
         <v>Futura carbon</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>123</v>
       </c>
@@ -6015,7 +6186,7 @@
         <v>Futura Carbon</v>
       </c>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>124</v>
       </c>
@@ -6054,7 +6225,7 @@
         <v>Go 139 Tufskin</v>
       </c>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>125</v>
       </c>
@@ -6093,7 +6264,7 @@
         <v>Isonic</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>126</v>
       </c>
@@ -6132,7 +6303,7 @@
         <v>iSonic 107 Carbon</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>127</v>
       </c>
@@ -6171,7 +6342,7 @@
         <v>iSonic 107 wood</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>128</v>
       </c>
@@ -6210,7 +6381,7 @@
         <v>iSonic 110 Carbon</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>129</v>
       </c>
@@ -6249,7 +6420,7 @@
         <v>Isonic 117</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>130</v>
       </c>
@@ -6288,7 +6459,7 @@
         <v>iSonic 117 wood</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>131</v>
       </c>
@@ -6327,7 +6498,7 @@
         <v>Isonic 120 carbon</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>132</v>
       </c>
@@ -6366,7 +6537,7 @@
         <v>iSonic 130 Carbon</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>133</v>
       </c>
@@ -6405,7 +6576,7 @@
         <v>Isonic 80 Wood</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>134</v>
       </c>
@@ -6444,7 +6615,7 @@
         <v>isonic 87 Carbon</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>135</v>
       </c>
@@ -6483,7 +6654,7 @@
         <v>iSonic 87 wood</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>136</v>
       </c>
@@ -6522,7 +6693,7 @@
         <v>Isonic 90 Carbon</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>137</v>
       </c>
@@ -6561,7 +6732,7 @@
         <v>iSonic 97 Carbon</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>138</v>
       </c>
@@ -6600,7 +6771,7 @@
         <v>Isonic 97 wood</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>139</v>
       </c>
@@ -6639,7 +6810,7 @@
         <v>Isonic carbon</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="14" t="s">
         <v>319</v>
       </c>
@@ -6681,7 +6852,7 @@
         <v>I-Sonic Speed 54</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>141</v>
       </c>
@@ -6720,7 +6891,7 @@
         <v>iSonic speed special w44</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>142</v>
       </c>
@@ -6759,7 +6930,7 @@
         <v>Isonic speed special W49</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>143</v>
       </c>
@@ -6798,7 +6969,7 @@
         <v>iSonic Speed Special W54</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>144</v>
       </c>
@@ -6834,7 +7005,7 @@
         <v>iSonics carbon</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>145</v>
       </c>
@@ -6870,7 +7041,7 @@
         <v>Kode 87 Wood Carbon</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>146</v>
       </c>
@@ -6909,7 +7080,7 @@
         <v>Kode FreeWave Wood</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>147</v>
       </c>
@@ -6942,7 +7113,7 @@
         <v>No idea</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>148</v>
       </c>
@@ -6981,7 +7152,7 @@
         <v>Slalom One</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>149</v>
       </c>
@@ -7020,7 +7191,7 @@
         <v>Speed special 58</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>150</v>
       </c>
@@ -7059,7 +7230,7 @@
         <v>Starboard AtomIQ 140</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>151</v>
       </c>
@@ -7098,7 +7269,7 @@
         <v>Ultrasonic Wood</v>
       </c>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>152</v>
       </c>
@@ -7137,8 +7308,978 @@
         <v>Windsup Touring Delux Inflatable</v>
       </c>
     </row>
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B155">
+        <v>153</v>
+      </c>
+      <c r="C155">
+        <v>2010</v>
+      </c>
+      <c r="D155" t="s">
+        <v>201</v>
+      </c>
+      <c r="E155" t="s">
+        <v>322</v>
+      </c>
+      <c r="F155" t="s">
+        <v>166</v>
+      </c>
+      <c r="G155" t="s">
+        <v>323</v>
+      </c>
+      <c r="H155">
+        <v>2007</v>
+      </c>
+      <c r="I155" t="s">
+        <v>26</v>
+      </c>
+      <c r="K155">
+        <v>7</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155" s="1" t="str">
+        <f t="shared" ref="M155:M181" si="0">HYPERLINK(_xlfn.CONCAT($F$1,C155),E155)</f>
+        <v>AllWave</v>
+      </c>
+    </row>
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B156">
+        <v>154</v>
+      </c>
+      <c r="C156">
+        <v>2625</v>
+      </c>
+      <c r="D156" t="s">
+        <v>201</v>
+      </c>
+      <c r="E156" t="s">
+        <v>324</v>
+      </c>
+      <c r="F156" t="s">
+        <v>105</v>
+      </c>
+      <c r="G156" t="s">
+        <v>325</v>
+      </c>
+      <c r="H156">
+        <v>2007</v>
+      </c>
+      <c r="I156" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156">
+        <v>3</v>
+      </c>
+      <c r="M156" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Eagle</v>
+      </c>
+    </row>
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B157">
+        <v>155</v>
+      </c>
+      <c r="C157">
+        <v>2240</v>
+      </c>
+      <c r="D157" t="s">
+        <v>201</v>
+      </c>
+      <c r="E157" t="s">
+        <v>326</v>
+      </c>
+      <c r="F157" t="s">
+        <v>327</v>
+      </c>
+      <c r="G157" t="s">
+        <v>117</v>
+      </c>
+      <c r="H157">
+        <v>2007</v>
+      </c>
+      <c r="I157" t="s">
+        <v>58</v>
+      </c>
+      <c r="K157">
+        <v>9</v>
+      </c>
+      <c r="L157">
+        <v>5</v>
+      </c>
+      <c r="M157" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Eagle 100</v>
+      </c>
+    </row>
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B158">
+        <v>156</v>
+      </c>
+      <c r="C158">
+        <v>3064</v>
+      </c>
+      <c r="D158" t="s">
+        <v>201</v>
+      </c>
+      <c r="E158" t="s">
+        <v>328</v>
+      </c>
+      <c r="F158" t="s">
+        <v>329</v>
+      </c>
+      <c r="G158" t="s">
+        <v>325</v>
+      </c>
+      <c r="H158">
+        <v>2007</v>
+      </c>
+      <c r="I158" t="s">
+        <v>58</v>
+      </c>
+      <c r="K158">
+        <v>14</v>
+      </c>
+      <c r="L158">
+        <v>5</v>
+      </c>
+      <c r="M158" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Eagle 126</v>
+      </c>
+    </row>
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B159">
+        <v>157</v>
+      </c>
+      <c r="C159">
+        <v>1904</v>
+      </c>
+      <c r="D159" t="s">
+        <v>201</v>
+      </c>
+      <c r="E159" t="s">
+        <v>330</v>
+      </c>
+      <c r="F159" t="s">
+        <v>331</v>
+      </c>
+      <c r="G159" t="s">
+        <v>89</v>
+      </c>
+      <c r="H159">
+        <v>2007</v>
+      </c>
+      <c r="I159" t="s">
+        <v>58</v>
+      </c>
+      <c r="K159">
+        <v>24</v>
+      </c>
+      <c r="L159">
+        <v>9</v>
+      </c>
+      <c r="M159" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon</v>
+      </c>
+    </row>
+    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B160">
+        <v>158</v>
+      </c>
+      <c r="C160">
+        <v>2409</v>
+      </c>
+      <c r="D160" t="s">
+        <v>201</v>
+      </c>
+      <c r="E160" t="s">
+        <v>332</v>
+      </c>
+      <c r="F160" t="s">
+        <v>333</v>
+      </c>
+      <c r="G160" t="s">
+        <v>79</v>
+      </c>
+      <c r="H160">
+        <v>2007</v>
+      </c>
+      <c r="I160" t="s">
+        <v>58</v>
+      </c>
+      <c r="K160">
+        <v>832</v>
+      </c>
+      <c r="L160">
+        <v>30</v>
+      </c>
+      <c r="M160" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon 105</v>
+      </c>
+    </row>
+    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B161">
+        <v>159</v>
+      </c>
+      <c r="C161">
+        <v>1874</v>
+      </c>
+      <c r="D161" t="s">
+        <v>201</v>
+      </c>
+      <c r="E161" t="s">
+        <v>334</v>
+      </c>
+      <c r="F161" t="s">
+        <v>335</v>
+      </c>
+      <c r="G161" t="s">
+        <v>336</v>
+      </c>
+      <c r="H161">
+        <v>2007</v>
+      </c>
+      <c r="I161" t="s">
+        <v>22</v>
+      </c>
+      <c r="K161">
+        <v>961</v>
+      </c>
+      <c r="L161">
+        <v>27</v>
+      </c>
+      <c r="M161" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon 125</v>
+      </c>
+    </row>
+    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B162">
+        <v>160</v>
+      </c>
+      <c r="C162">
+        <v>3083</v>
+      </c>
+      <c r="D162" t="s">
+        <v>201</v>
+      </c>
+      <c r="E162" t="s">
+        <v>337</v>
+      </c>
+      <c r="F162" t="s">
+        <v>338</v>
+      </c>
+      <c r="G162" t="s">
+        <v>339</v>
+      </c>
+      <c r="H162">
+        <v>2007</v>
+      </c>
+      <c r="I162" t="s">
+        <v>67</v>
+      </c>
+      <c r="K162">
+        <v>33</v>
+      </c>
+      <c r="L162">
+        <v>5</v>
+      </c>
+      <c r="M162" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon 145</v>
+      </c>
+    </row>
+    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B163">
+        <v>161</v>
+      </c>
+      <c r="C163">
+        <v>1905</v>
+      </c>
+      <c r="D163" t="s">
+        <v>201</v>
+      </c>
+      <c r="E163" t="s">
+        <v>340</v>
+      </c>
+      <c r="F163" t="s">
+        <v>331</v>
+      </c>
+      <c r="G163" t="s">
+        <v>89</v>
+      </c>
+      <c r="H163">
+        <v>2007</v>
+      </c>
+      <c r="I163" t="s">
+        <v>58</v>
+      </c>
+      <c r="K163">
+        <v>2396</v>
+      </c>
+      <c r="L163">
+        <v>61</v>
+      </c>
+      <c r="M163" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon 90</v>
+      </c>
+    </row>
+    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B164">
+        <v>162</v>
+      </c>
+      <c r="C164">
+        <v>2554</v>
+      </c>
+      <c r="D164" t="s">
+        <v>201</v>
+      </c>
+      <c r="E164" t="s">
+        <v>341</v>
+      </c>
+      <c r="F164" t="s">
+        <v>331</v>
+      </c>
+      <c r="G164" t="s">
+        <v>89</v>
+      </c>
+      <c r="H164">
+        <v>2007</v>
+      </c>
+      <c r="I164" t="s">
+        <v>58</v>
+      </c>
+      <c r="K164">
+        <v>19</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon 90 Proto</v>
+      </c>
+    </row>
+    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B165">
+        <v>163</v>
+      </c>
+      <c r="C165">
+        <v>3737</v>
+      </c>
+      <c r="D165" t="s">
+        <v>201</v>
+      </c>
+      <c r="E165" t="s">
+        <v>342</v>
+      </c>
+      <c r="F165" t="s">
+        <v>343</v>
+      </c>
+      <c r="G165" t="s">
+        <v>344</v>
+      </c>
+      <c r="H165">
+        <v>2007</v>
+      </c>
+      <c r="I165" t="s">
+        <v>227</v>
+      </c>
+      <c r="K165">
+        <v>24</v>
+      </c>
+      <c r="L165">
+        <v>8</v>
+      </c>
+      <c r="M165" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Formula TT</v>
+      </c>
+    </row>
+    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B166">
+        <v>164</v>
+      </c>
+      <c r="C166">
+        <v>4185</v>
+      </c>
+      <c r="D166" t="s">
+        <v>201</v>
+      </c>
+      <c r="E166" t="s">
+        <v>345</v>
+      </c>
+      <c r="F166" t="s">
+        <v>346</v>
+      </c>
+      <c r="G166" t="s">
+        <v>347</v>
+      </c>
+      <c r="H166">
+        <v>2007</v>
+      </c>
+      <c r="I166" t="s">
+        <v>22</v>
+      </c>
+      <c r="K166">
+        <v>25</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon prototype</v>
+      </c>
+    </row>
+    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B167">
+        <v>165</v>
+      </c>
+      <c r="C167">
+        <v>2927</v>
+      </c>
+      <c r="D167" t="s">
+        <v>201</v>
+      </c>
+      <c r="E167" t="s">
+        <v>348</v>
+      </c>
+      <c r="F167" t="s">
+        <v>333</v>
+      </c>
+      <c r="G167" t="s">
+        <v>42</v>
+      </c>
+      <c r="H167">
+        <v>2007</v>
+      </c>
+      <c r="I167" t="s">
+        <v>58</v>
+      </c>
+      <c r="K167">
+        <v>71</v>
+      </c>
+      <c r="L167">
+        <v>3</v>
+      </c>
+      <c r="M167" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon SL 105</v>
+      </c>
+    </row>
+    <row r="168" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B168">
+        <v>166</v>
+      </c>
+      <c r="C168">
+        <v>2039</v>
+      </c>
+      <c r="D168" t="s">
+        <v>201</v>
+      </c>
+      <c r="E168" t="s">
+        <v>349</v>
+      </c>
+      <c r="F168" t="s">
+        <v>338</v>
+      </c>
+      <c r="G168" t="s">
+        <v>339</v>
+      </c>
+      <c r="H168">
+        <v>2007</v>
+      </c>
+      <c r="I168" t="s">
+        <v>67</v>
+      </c>
+      <c r="K168">
+        <v>41</v>
+      </c>
+      <c r="L168">
+        <v>3</v>
+      </c>
+      <c r="M168" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon SL 145</v>
+      </c>
+    </row>
+    <row r="169" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B169">
+        <v>167</v>
+      </c>
+      <c r="C169">
+        <v>2391</v>
+      </c>
+      <c r="D169" t="s">
+        <v>201</v>
+      </c>
+      <c r="E169" t="s">
+        <v>350</v>
+      </c>
+      <c r="F169" t="s">
+        <v>331</v>
+      </c>
+      <c r="G169" t="s">
+        <v>89</v>
+      </c>
+      <c r="H169">
+        <v>2007</v>
+      </c>
+      <c r="I169" t="s">
+        <v>58</v>
+      </c>
+      <c r="K169">
+        <v>140</v>
+      </c>
+      <c r="L169">
+        <v>6</v>
+      </c>
+      <c r="M169" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon SL90</v>
+      </c>
+    </row>
+    <row r="170" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B170">
+        <v>168</v>
+      </c>
+      <c r="C170">
+        <v>2802</v>
+      </c>
+      <c r="D170" t="s">
+        <v>201</v>
+      </c>
+      <c r="E170" t="s">
+        <v>351</v>
+      </c>
+      <c r="F170" t="s">
+        <v>352</v>
+      </c>
+      <c r="G170" t="s">
+        <v>79</v>
+      </c>
+      <c r="H170">
+        <v>2007</v>
+      </c>
+      <c r="I170" t="s">
+        <v>58</v>
+      </c>
+      <c r="K170">
+        <v>45</v>
+      </c>
+      <c r="L170">
+        <v>2</v>
+      </c>
+      <c r="M170" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Slalom 105</v>
+      </c>
+    </row>
+    <row r="171" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B171">
+        <v>169</v>
+      </c>
+      <c r="C171">
+        <v>2928</v>
+      </c>
+      <c r="D171" t="s">
+        <v>201</v>
+      </c>
+      <c r="E171" t="s">
+        <v>353</v>
+      </c>
+      <c r="F171" t="s">
+        <v>105</v>
+      </c>
+      <c r="G171" t="s">
+        <v>354</v>
+      </c>
+      <c r="H171">
+        <v>2007</v>
+      </c>
+      <c r="I171" t="s">
+        <v>43</v>
+      </c>
+      <c r="K171">
+        <v>2</v>
+      </c>
+      <c r="M171" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Falcon Speed</v>
+      </c>
+    </row>
+    <row r="172" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B172">
+        <v>170</v>
+      </c>
+      <c r="C172">
+        <v>12052</v>
+      </c>
+      <c r="D172" t="s">
+        <v>201</v>
+      </c>
+      <c r="E172" t="s">
+        <v>355</v>
+      </c>
+      <c r="F172" t="s">
+        <v>356</v>
+      </c>
+      <c r="G172" t="s">
+        <v>357</v>
+      </c>
+      <c r="H172">
+        <v>2007</v>
+      </c>
+      <c r="I172" t="s">
+        <v>61</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Freemove</v>
+      </c>
+    </row>
+    <row r="173" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B173">
+        <v>171</v>
+      </c>
+      <c r="C173">
+        <v>4319</v>
+      </c>
+      <c r="D173" t="s">
+        <v>201</v>
+      </c>
+      <c r="E173" t="s">
+        <v>358</v>
+      </c>
+      <c r="F173" t="s">
+        <v>359</v>
+      </c>
+      <c r="G173" t="s">
+        <v>175</v>
+      </c>
+      <c r="H173">
+        <v>2007</v>
+      </c>
+      <c r="I173" t="s">
+        <v>26</v>
+      </c>
+      <c r="K173">
+        <v>5</v>
+      </c>
+      <c r="L173">
+        <v>2</v>
+      </c>
+      <c r="M173" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Freewave</v>
+      </c>
+    </row>
+    <row r="174" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B174">
+        <v>172</v>
+      </c>
+      <c r="C174">
+        <v>2317</v>
+      </c>
+      <c r="D174" t="s">
+        <v>201</v>
+      </c>
+      <c r="E174" t="s">
+        <v>360</v>
+      </c>
+      <c r="F174" t="s">
+        <v>361</v>
+      </c>
+      <c r="G174" t="s">
+        <v>232</v>
+      </c>
+      <c r="H174">
+        <v>2007</v>
+      </c>
+      <c r="I174" t="s">
+        <v>26</v>
+      </c>
+      <c r="K174">
+        <v>20</v>
+      </c>
+      <c r="L174">
+        <v>10</v>
+      </c>
+      <c r="M174" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Freewave 104</v>
+      </c>
+    </row>
+    <row r="175" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B175">
+        <v>173</v>
+      </c>
+      <c r="C175">
+        <v>2379</v>
+      </c>
+      <c r="D175" t="s">
+        <v>201</v>
+      </c>
+      <c r="E175" t="s">
+        <v>362</v>
+      </c>
+      <c r="F175" t="s">
+        <v>363</v>
+      </c>
+      <c r="G175" t="s">
+        <v>364</v>
+      </c>
+      <c r="H175">
+        <v>2007</v>
+      </c>
+      <c r="I175" t="s">
+        <v>26</v>
+      </c>
+      <c r="K175">
+        <v>63</v>
+      </c>
+      <c r="L175">
+        <v>5</v>
+      </c>
+      <c r="M175" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Freewave 86</v>
+      </c>
+    </row>
+    <row r="176" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B176">
+        <v>174</v>
+      </c>
+      <c r="C176">
+        <v>2769</v>
+      </c>
+      <c r="D176" t="s">
+        <v>201</v>
+      </c>
+      <c r="E176" t="s">
+        <v>365</v>
+      </c>
+      <c r="F176" t="s">
+        <v>366</v>
+      </c>
+      <c r="G176" t="s">
+        <v>357</v>
+      </c>
+      <c r="H176">
+        <v>2007</v>
+      </c>
+      <c r="I176" t="s">
+        <v>26</v>
+      </c>
+      <c r="K176">
+        <v>103</v>
+      </c>
+      <c r="L176">
+        <v>10</v>
+      </c>
+      <c r="M176" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Freewave 95</v>
+      </c>
+    </row>
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B177">
+        <v>175</v>
+      </c>
+      <c r="C177">
+        <v>2239</v>
+      </c>
+      <c r="D177" t="s">
+        <v>201</v>
+      </c>
+      <c r="E177" t="s">
+        <v>367</v>
+      </c>
+      <c r="F177" t="s">
+        <v>368</v>
+      </c>
+      <c r="G177" t="s">
+        <v>369</v>
+      </c>
+      <c r="H177">
+        <v>2007</v>
+      </c>
+      <c r="I177" t="s">
+        <v>58</v>
+      </c>
+      <c r="K177">
+        <v>84</v>
+      </c>
+      <c r="L177">
+        <v>11</v>
+      </c>
+      <c r="M177" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hawk 108</v>
+      </c>
+    </row>
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B178">
+        <v>176</v>
+      </c>
+      <c r="C178">
+        <v>2227</v>
+      </c>
+      <c r="D178" t="s">
+        <v>201</v>
+      </c>
+      <c r="E178" t="s">
+        <v>370</v>
+      </c>
+      <c r="F178" t="s">
+        <v>371</v>
+      </c>
+      <c r="G178" t="s">
+        <v>372</v>
+      </c>
+      <c r="H178">
+        <v>2007</v>
+      </c>
+      <c r="I178" t="s">
+        <v>58</v>
+      </c>
+      <c r="K178">
+        <v>6</v>
+      </c>
+      <c r="L178">
+        <v>5</v>
+      </c>
+      <c r="M178" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Hawk 123</v>
+      </c>
+    </row>
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B179">
+        <v>177</v>
+      </c>
+      <c r="C179">
+        <v>3031</v>
+      </c>
+      <c r="D179" t="s">
+        <v>201</v>
+      </c>
+      <c r="E179" t="s">
+        <v>373</v>
+      </c>
+      <c r="F179" t="s">
+        <v>374</v>
+      </c>
+      <c r="G179" t="s">
+        <v>339</v>
+      </c>
+      <c r="H179">
+        <v>2007</v>
+      </c>
+      <c r="I179" t="s">
+        <v>22</v>
+      </c>
+      <c r="K179">
+        <v>25</v>
+      </c>
+      <c r="L179">
+        <v>6</v>
+      </c>
+      <c r="M179" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Shark</v>
+      </c>
+    </row>
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B180">
+        <v>178</v>
+      </c>
+      <c r="C180">
+        <v>3310</v>
+      </c>
+      <c r="D180" t="s">
+        <v>201</v>
+      </c>
+      <c r="E180" t="s">
+        <v>375</v>
+      </c>
+      <c r="F180" t="s">
+        <v>376</v>
+      </c>
+      <c r="G180" t="s">
+        <v>35</v>
+      </c>
+      <c r="H180">
+        <v>2007</v>
+      </c>
+      <c r="I180" t="s">
+        <v>22</v>
+      </c>
+      <c r="K180">
+        <v>84</v>
+      </c>
+      <c r="L180">
+        <v>9</v>
+      </c>
+      <c r="M180" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Shark 130 Ltd</v>
+      </c>
+    </row>
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B181">
+        <v>179</v>
+      </c>
+      <c r="C181">
+        <v>3215</v>
+      </c>
+      <c r="D181" t="s">
+        <v>201</v>
+      </c>
+      <c r="E181" t="s">
+        <v>377</v>
+      </c>
+      <c r="F181" t="s">
+        <v>378</v>
+      </c>
+      <c r="G181" t="s">
+        <v>339</v>
+      </c>
+      <c r="H181">
+        <v>2007</v>
+      </c>
+      <c r="I181" t="s">
+        <v>22</v>
+      </c>
+      <c r="K181">
+        <v>24</v>
+      </c>
+      <c r="L181">
+        <v>4</v>
+      </c>
+      <c r="M181" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Shark HRS 145 L</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:M2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}"/>
+  <autoFilter ref="A2:M2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M181">
+      <sortCondition ref="B2"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7147,9 +8288,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A702A5F9-18CA-47B5-B545-037F63A1FD14}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="8">
         <v>2013</v>
       </c>
@@ -7163,7 +8304,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -7174,7 +8315,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>208</v>
       </c>
@@ -7186,7 +8327,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>209</v>
       </c>
@@ -7198,7 +8339,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>210</v>
       </c>
@@ -7210,7 +8351,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>211</v>
       </c>
@@ -7222,7 +8363,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>207</v>
       </c>
@@ -7234,7 +8375,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>205</v>
       </c>
@@ -7246,7 +8387,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>204</v>
       </c>
@@ -7258,7 +8399,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>203</v>
       </c>
@@ -7270,7 +8411,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>202</v>
       </c>
@@ -7282,7 +8423,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>201</v>
       </c>
@@ -7294,7 +8435,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>200</v>
       </c>
@@ -7306,7 +8447,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
@@ -7318,7 +8459,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D20" s="1" t="s">
         <v>212</v>
       </c>
@@ -7340,94 +8481,94 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467583F9-C105-4DC5-AB97-B32AA9231D3E}">
   <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2001</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2002</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2003</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2004</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2005</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2006</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2007</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2008</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2009</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2010</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2011</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2012</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2013</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2014</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2015</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2016</v>
       </c>

--- a/GPS-Speedsurfing-Board-Stats.xlsx
+++ b/GPS-Speedsurfing-Board-Stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Documents\bjorn76\WS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EFCAE7-DFED-4F4F-9EA4-C5B23D88239C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DAE2BC-FCC7-4E01-BEE4-086A357E3E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="ddl" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Stats'!$A$2:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Board Stats'!$A$2:$L$2</definedName>
     <definedName name="rYear">ddl!$A$2:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="410">
   <si>
     <t>#</t>
   </si>
@@ -995,9 +995,6 @@
     <t>Special / Longboard</t>
   </si>
   <si>
-    <t>Sport</t>
-  </si>
-  <si>
     <t>User</t>
   </si>
   <si>
@@ -1179,6 +1176,102 @@
   </si>
   <si>
     <t>75 x 263 cm</t>
+  </si>
+  <si>
+    <t>Attitude Inspiro 79</t>
+  </si>
+  <si>
+    <t>78 x 252 cm</t>
+  </si>
+  <si>
+    <t>136 l</t>
+  </si>
+  <si>
+    <t>Attitude Inspiro 87</t>
+  </si>
+  <si>
+    <t>Formula 98 N.T.</t>
+  </si>
+  <si>
+    <t>95 x 260 cm</t>
+  </si>
+  <si>
+    <t>158 l</t>
+  </si>
+  <si>
+    <t>GT Special 54</t>
+  </si>
+  <si>
+    <t>54 x 242 cm</t>
+  </si>
+  <si>
+    <t>78 l</t>
+  </si>
+  <si>
+    <t>GT Special 73</t>
+  </si>
+  <si>
+    <t>73 x 258 cm</t>
+  </si>
+  <si>
+    <t>GT Special 86</t>
+  </si>
+  <si>
+    <t>85 x 260 cm</t>
+  </si>
+  <si>
+    <t>Kauli Pro 81</t>
+  </si>
+  <si>
+    <t>55 x 240 cm</t>
+  </si>
+  <si>
+    <t>81 l</t>
+  </si>
+  <si>
+    <t>Maxx Ride 104</t>
+  </si>
+  <si>
+    <t>66 x 250 cm</t>
+  </si>
+  <si>
+    <t>Maxx Ride 92</t>
+  </si>
+  <si>
+    <t>62 x 250 cm</t>
+  </si>
+  <si>
+    <t>Mx 57</t>
+  </si>
+  <si>
+    <t>58 x 250 cm</t>
+  </si>
+  <si>
+    <t>Type F 64</t>
+  </si>
+  <si>
+    <t>64 x 256 cm</t>
+  </si>
+  <si>
+    <t>106 l</t>
+  </si>
+  <si>
+    <t>Type F 75</t>
+  </si>
+  <si>
+    <t>75 x 262 cm</t>
+  </si>
+  <si>
+    <t>Type F 85</t>
+  </si>
+  <si>
+    <t>85 x 262 cm</t>
+  </si>
+  <si>
+    <t>86 x 255 cm</t>
+  </si>
+  <si>
+    <t>153 l</t>
   </si>
 </sst>
 </file>
@@ -1323,13 +1416,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>409575</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>14540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>115474</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>48479</xdr:rowOff>
@@ -1367,13 +1460,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>388606</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>420177</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>29307</xdr:rowOff>
@@ -1675,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="14" bestFit="1" customWidth="1"/>
@@ -1685,19 +1778,18 @@
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.109375" customWidth="1"/>
-    <col min="13" max="13" width="26.33203125" customWidth="1"/>
+    <col min="12" max="12" width="26.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
       <c r="F1" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -1724,19 +1816,16 @@
         <v>7</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>317</v>
+        <v>8</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -1761,18 +1850,18 @@
       <c r="I3" t="s">
         <v>14</v>
       </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
       <c r="K3">
-        <v>9</v>
-      </c>
-      <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" s="1" t="str">
+      <c r="L3" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C3),E3)</f>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -1797,18 +1886,18 @@
       <c r="I4" t="s">
         <v>14</v>
       </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
       <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
         <v>2</v>
       </c>
-      <c r="M4" s="1" t="str">
+      <c r="L4" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C4),E4)</f>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1833,18 +1922,18 @@
       <c r="I5" t="s">
         <v>14</v>
       </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
       <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
         <v>2</v>
       </c>
-      <c r="M5" s="1" t="str">
+      <c r="L5" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C5),E5)</f>
         <v>Custom Aurelio Verdi</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1869,18 +1958,18 @@
       <c r="I6" t="s">
         <v>22</v>
       </c>
+      <c r="J6">
+        <v>83</v>
+      </c>
       <c r="K6">
-        <v>83</v>
-      </c>
-      <c r="L6">
         <v>1</v>
       </c>
-      <c r="M6" s="1" t="str">
+      <c r="L6" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C6),E6)</f>
         <v>Fire Storm Wood V2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1905,18 +1994,18 @@
       <c r="I7" t="s">
         <v>26</v>
       </c>
+      <c r="J7">
+        <v>53</v>
+      </c>
       <c r="K7">
-        <v>53</v>
-      </c>
-      <c r="L7">
         <v>3</v>
       </c>
-      <c r="M7" s="1" t="str">
+      <c r="L7" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C7),E7)</f>
         <v>Firemove Ltd V2 102</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1941,18 +2030,18 @@
       <c r="I8" t="s">
         <v>26</v>
       </c>
+      <c r="J8">
+        <v>13</v>
+      </c>
       <c r="K8">
-        <v>13</v>
-      </c>
-      <c r="L8">
         <v>4</v>
       </c>
-      <c r="M8" s="1" t="str">
+      <c r="L8" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C8),E8)</f>
         <v>Firemove Ltd V2 112</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1977,18 +2066,18 @@
       <c r="I9" t="s">
         <v>26</v>
       </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
       <c r="K9">
-        <v>6</v>
-      </c>
-      <c r="L9">
         <v>2</v>
       </c>
-      <c r="M9" s="1" t="str">
+      <c r="L9" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C9),E9)</f>
         <v>Firemove Ltd V2 122</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -2013,18 +2102,18 @@
       <c r="I10" t="s">
         <v>26</v>
       </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
       <c r="K10">
-        <v>4</v>
-      </c>
-      <c r="L10">
         <v>2</v>
       </c>
-      <c r="M10" s="1" t="str">
+      <c r="L10" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C10),E10)</f>
         <v>Firemove Ltd V2 130</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
@@ -2049,18 +2138,18 @@
       <c r="I11" t="s">
         <v>26</v>
       </c>
+      <c r="J11">
+        <v>60</v>
+      </c>
       <c r="K11">
-        <v>60</v>
-      </c>
-      <c r="L11">
         <v>5</v>
       </c>
-      <c r="M11" s="1" t="str">
+      <c r="L11" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C11),E11)</f>
         <v>Firemove Ltd V2 140</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -2085,18 +2174,18 @@
       <c r="I12" t="s">
         <v>26</v>
       </c>
+      <c r="J12">
+        <v>11</v>
+      </c>
       <c r="K12">
-        <v>11</v>
-      </c>
-      <c r="L12">
         <v>1</v>
       </c>
-      <c r="M12" s="1" t="str">
+      <c r="L12" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C12),E12)</f>
         <v>Firemove V2 Wood</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>11</v>
       </c>
@@ -2121,15 +2210,15 @@
       <c r="I13" t="s">
         <v>43</v>
       </c>
-      <c r="K13">
+      <c r="J13">
         <v>2</v>
       </c>
-      <c r="M13" s="1" t="str">
+      <c r="L13" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C13),E13)</f>
         <v>firestorm 111</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>12</v>
       </c>
@@ -2154,18 +2243,18 @@
       <c r="I14" t="s">
         <v>22</v>
       </c>
+      <c r="J14">
+        <v>44</v>
+      </c>
       <c r="K14">
-        <v>44</v>
-      </c>
-      <c r="L14">
         <v>1</v>
       </c>
-      <c r="M14" s="1" t="str">
+      <c r="L14" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C14),E14)</f>
         <v>Firestorm LTD</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>13</v>
       </c>
@@ -2190,18 +2279,18 @@
       <c r="I15" t="s">
         <v>22</v>
       </c>
+      <c r="J15">
+        <v>73</v>
+      </c>
       <c r="K15">
-        <v>73</v>
-      </c>
-      <c r="L15">
         <v>1</v>
       </c>
-      <c r="M15" s="1" t="str">
+      <c r="L15" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C15),E15)</f>
         <v>Firestorm LTD V2</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>14</v>
       </c>
@@ -2226,18 +2315,18 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
+      <c r="J16">
+        <v>52</v>
+      </c>
       <c r="K16">
-        <v>52</v>
-      </c>
-      <c r="L16">
         <v>1</v>
       </c>
-      <c r="M16" s="1" t="str">
+      <c r="L16" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C16),E16)</f>
         <v>Firewave LTD</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -2262,15 +2351,15 @@
       <c r="I17" t="s">
         <v>22</v>
       </c>
-      <c r="K17">
+      <c r="J17">
         <v>1</v>
       </c>
-      <c r="M17" s="1" t="str">
+      <c r="L17" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C17),E17)</f>
         <v>freerace</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>16</v>
       </c>
@@ -2295,15 +2384,15 @@
       <c r="I18" t="s">
         <v>58</v>
       </c>
-      <c r="K18">
+      <c r="J18">
         <v>5</v>
       </c>
-      <c r="M18" s="1" t="str">
+      <c r="L18" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C18),E18)</f>
         <v>proto Firestorm V3 #053</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>17</v>
       </c>
@@ -2328,18 +2417,18 @@
       <c r="I19" t="s">
         <v>61</v>
       </c>
+      <c r="J19">
+        <v>5</v>
+      </c>
       <c r="K19">
-        <v>5</v>
-      </c>
-      <c r="L19">
         <v>1</v>
       </c>
-      <c r="M19" s="1" t="str">
+      <c r="L19" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C19),E19)</f>
         <v>Proto X-Fire 98 V7</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>18</v>
       </c>
@@ -2364,15 +2453,15 @@
       <c r="I20" t="s">
         <v>43</v>
       </c>
-      <c r="K20">
+      <c r="J20">
         <v>5</v>
       </c>
-      <c r="M20" s="1" t="str">
+      <c r="L20" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C20),E20)</f>
         <v>Slalom</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>19</v>
       </c>
@@ -2397,15 +2486,15 @@
       <c r="I21" t="s">
         <v>67</v>
       </c>
-      <c r="K21">
+      <c r="J21">
         <v>4</v>
       </c>
-      <c r="M21" s="1" t="str">
+      <c r="L21" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C21),E21)</f>
         <v>Slalom Large Proto</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20</v>
       </c>
@@ -2430,18 +2519,18 @@
       <c r="I22" t="s">
         <v>14</v>
       </c>
+      <c r="J22">
+        <v>28</v>
+      </c>
       <c r="K22">
-        <v>28</v>
-      </c>
-      <c r="L22">
         <v>2</v>
       </c>
-      <c r="M22" s="1" t="str">
+      <c r="L22" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C22),E22)</f>
         <v>Speed 41</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>21</v>
       </c>
@@ -2466,18 +2555,18 @@
       <c r="I23" t="s">
         <v>14</v>
       </c>
+      <c r="J23">
+        <v>35</v>
+      </c>
       <c r="K23">
-        <v>35</v>
-      </c>
-      <c r="L23">
         <v>3</v>
       </c>
-      <c r="M23" s="1" t="str">
+      <c r="L23" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C23),E23)</f>
         <v>Speed 43</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>22</v>
       </c>
@@ -2502,18 +2591,18 @@
       <c r="I24" t="s">
         <v>14</v>
       </c>
+      <c r="J24">
+        <v>9</v>
+      </c>
       <c r="K24">
-        <v>9</v>
-      </c>
-      <c r="L24">
         <v>1</v>
       </c>
-      <c r="M24" s="1" t="str">
+      <c r="L24" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C24),E24)</f>
         <v>speed board</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>23</v>
       </c>
@@ -2538,18 +2627,18 @@
       <c r="I25" t="s">
         <v>58</v>
       </c>
+      <c r="J25">
+        <v>23</v>
+      </c>
       <c r="K25">
-        <v>23</v>
-      </c>
-      <c r="L25">
         <v>2</v>
       </c>
-      <c r="M25" s="1" t="str">
+      <c r="L25" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C25),E25)</f>
         <v>x fire</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>24</v>
       </c>
@@ -2574,18 +2663,18 @@
       <c r="I26" t="s">
         <v>58</v>
       </c>
+      <c r="J26">
+        <v>612</v>
+      </c>
       <c r="K26">
-        <v>612</v>
-      </c>
-      <c r="L26">
         <v>17</v>
       </c>
-      <c r="M26" s="1" t="str">
+      <c r="L26" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C26),E26)</f>
         <v>X-Fire LTD V6 105</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>25</v>
       </c>
@@ -2610,18 +2699,18 @@
       <c r="I27" t="s">
         <v>58</v>
       </c>
+      <c r="J27">
+        <v>840</v>
+      </c>
       <c r="K27">
-        <v>840</v>
-      </c>
-      <c r="L27">
         <v>24</v>
       </c>
-      <c r="M27" s="1" t="str">
+      <c r="L27" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C27),E27)</f>
         <v>X-Fire LTD V6 114</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>26</v>
       </c>
@@ -2646,18 +2735,18 @@
       <c r="I28" t="s">
         <v>22</v>
       </c>
+      <c r="J28">
+        <v>134</v>
+      </c>
       <c r="K28">
-        <v>134</v>
-      </c>
-      <c r="L28">
         <v>15</v>
       </c>
-      <c r="M28" s="1" t="str">
+      <c r="L28" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C28),E28)</f>
         <v>X-Fire LTD V6 122</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>27</v>
       </c>
@@ -2682,20 +2771,20 @@
       <c r="I29" t="s">
         <v>22</v>
       </c>
+      <c r="J29">
+        <v>64</v>
+      </c>
       <c r="K29">
-        <v>64</v>
-      </c>
-      <c r="L29">
         <v>5</v>
       </c>
-      <c r="M29" s="1" t="str">
+      <c r="L29" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C29),E29)</f>
         <v>X-Fire LTD V6 129</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B30" s="6">
         <v>28</v>
@@ -2721,19 +2810,18 @@
       <c r="I30" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6">
+        <v>326</v>
+      </c>
       <c r="K30" s="6">
-        <v>326</v>
-      </c>
-      <c r="L30" s="6">
         <v>13</v>
       </c>
-      <c r="M30" s="11" t="str">
+      <c r="L30" s="11" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C30),E30)</f>
         <v>X-Fire LTD V6 90</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>29</v>
       </c>
@@ -2758,18 +2846,18 @@
       <c r="I31" t="s">
         <v>61</v>
       </c>
+      <c r="J31">
+        <v>479</v>
+      </c>
       <c r="K31">
-        <v>479</v>
-      </c>
-      <c r="L31">
         <v>18</v>
       </c>
-      <c r="M31" s="1" t="str">
+      <c r="L31" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C31),E31)</f>
         <v>X-Fire LTD V6 98</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>30</v>
       </c>
@@ -2794,18 +2882,18 @@
       <c r="I32" t="s">
         <v>58</v>
       </c>
+      <c r="J32">
+        <v>29</v>
+      </c>
       <c r="K32">
-        <v>29</v>
-      </c>
-      <c r="L32">
         <v>4</v>
       </c>
-      <c r="M32" s="1" t="str">
+      <c r="L32" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C32),E32)</f>
         <v>X-Fire LTD V7 105</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>31</v>
       </c>
@@ -2830,18 +2918,18 @@
       <c r="I33" t="s">
         <v>58</v>
       </c>
+      <c r="J33">
+        <v>48</v>
+      </c>
       <c r="K33">
-        <v>48</v>
-      </c>
-      <c r="L33">
         <v>4</v>
       </c>
-      <c r="M33" s="1" t="str">
+      <c r="L33" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C33),E33)</f>
         <v>X-Fire LTD V7 114</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>32</v>
       </c>
@@ -2866,18 +2954,18 @@
       <c r="I34" t="s">
         <v>22</v>
       </c>
+      <c r="J34">
+        <v>160</v>
+      </c>
       <c r="K34">
-        <v>160</v>
-      </c>
-      <c r="L34">
         <v>3</v>
       </c>
-      <c r="M34" s="1" t="str">
+      <c r="L34" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C34),E34)</f>
         <v>X-Fire LTD V7 122</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>33</v>
       </c>
@@ -2902,18 +2990,18 @@
       <c r="I35" t="s">
         <v>22</v>
       </c>
+      <c r="J35">
+        <v>7</v>
+      </c>
       <c r="K35">
-        <v>7</v>
-      </c>
-      <c r="L35">
         <v>1</v>
       </c>
-      <c r="M35" s="1" t="str">
+      <c r="L35" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C35),E35)</f>
         <v>X-Fire LTD V7 129</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>34</v>
       </c>
@@ -2938,18 +3026,18 @@
       <c r="I36" t="s">
         <v>61</v>
       </c>
+      <c r="J36">
+        <v>31</v>
+      </c>
       <c r="K36">
-        <v>31</v>
-      </c>
-      <c r="L36">
         <v>1</v>
       </c>
-      <c r="M36" s="1" t="str">
+      <c r="L36" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C36),E36)</f>
         <v>X-Fire LTD V7 80</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>35</v>
       </c>
@@ -2974,18 +3062,18 @@
       <c r="I37" t="s">
         <v>61</v>
       </c>
+      <c r="J37">
+        <v>42</v>
+      </c>
       <c r="K37">
-        <v>42</v>
-      </c>
-      <c r="L37">
         <v>1</v>
       </c>
-      <c r="M37" s="1" t="str">
+      <c r="L37" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C37),E37)</f>
         <v>X-Fire LTD V7 90</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>36</v>
       </c>
@@ -3010,18 +3098,18 @@
       <c r="I38" t="s">
         <v>58</v>
       </c>
+      <c r="J38">
+        <v>70</v>
+      </c>
       <c r="K38">
-        <v>70</v>
-      </c>
-      <c r="L38">
         <v>3</v>
       </c>
-      <c r="M38" s="1" t="str">
+      <c r="L38" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C38),E38)</f>
         <v>X-Fire LTD V7 98</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>37</v>
       </c>
@@ -3046,20 +3134,20 @@
       <c r="I39" t="s">
         <v>22</v>
       </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
       <c r="K39">
-        <v>2</v>
-      </c>
-      <c r="L39">
         <v>1</v>
       </c>
-      <c r="M39" s="1" t="str">
+      <c r="L39" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C39),E39)</f>
         <v>X-Fire V5 LTD 128</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" s="9">
         <v>38</v>
@@ -3085,19 +3173,18 @@
       <c r="I40" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="J40" s="9"/>
+      <c r="J40" s="9">
+        <v>75</v>
+      </c>
       <c r="K40" s="9">
-        <v>75</v>
-      </c>
-      <c r="L40" s="9">
         <v>3</v>
       </c>
-      <c r="M40" s="10" t="str">
+      <c r="L40" s="10" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C40),E40)</f>
         <v>XiFire LTD V6 90</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>39</v>
       </c>
@@ -3122,18 +3209,18 @@
       <c r="I41" t="s">
         <v>14</v>
       </c>
+      <c r="J41">
+        <v>17</v>
+      </c>
       <c r="K41">
-        <v>17</v>
-      </c>
-      <c r="L41">
         <v>2</v>
       </c>
-      <c r="M41" s="1" t="str">
+      <c r="L41" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C41),E41)</f>
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>40</v>
       </c>
@@ -3158,18 +3245,18 @@
       <c r="I42" t="s">
         <v>26</v>
       </c>
+      <c r="J42">
+        <v>7</v>
+      </c>
       <c r="K42">
-        <v>7</v>
-      </c>
-      <c r="L42">
         <v>1</v>
       </c>
-      <c r="M42" s="1" t="str">
+      <c r="L42" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C42),E42)</f>
         <v>Firemove</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>41</v>
       </c>
@@ -3194,12 +3281,12 @@
       <c r="I43" t="s">
         <v>58</v>
       </c>
-      <c r="M43" s="1" t="str">
+      <c r="L43" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C43),E43)</f>
         <v>firemove</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
       <c r="B44">
         <v>42</v>
@@ -3225,18 +3312,18 @@
       <c r="I44" t="s">
         <v>58</v>
       </c>
+      <c r="J44">
+        <v>4</v>
+      </c>
       <c r="K44">
-        <v>4</v>
-      </c>
-      <c r="L44">
         <v>2</v>
       </c>
-      <c r="M44" s="1" t="str">
+      <c r="L44" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C44),E44)</f>
         <v>FireMove 120 LTD</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>43</v>
       </c>
@@ -3261,18 +3348,18 @@
       <c r="I45" t="s">
         <v>22</v>
       </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
       <c r="K45">
-        <v>4</v>
-      </c>
-      <c r="L45">
         <v>2</v>
       </c>
-      <c r="M45" s="1" t="str">
+      <c r="L45" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C45),E45)</f>
         <v>FireMove 140 LTD</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>44</v>
       </c>
@@ -3297,18 +3384,18 @@
       <c r="I46" t="s">
         <v>22</v>
       </c>
+      <c r="J46">
+        <v>7</v>
+      </c>
       <c r="K46">
-        <v>7</v>
-      </c>
-      <c r="L46">
         <v>1</v>
       </c>
-      <c r="M46" s="1" t="str">
+      <c r="L46" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C46),E46)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>45</v>
       </c>
@@ -3333,18 +3420,18 @@
       <c r="I47" t="s">
         <v>43</v>
       </c>
+      <c r="J47">
+        <v>62</v>
+      </c>
       <c r="K47">
-        <v>62</v>
-      </c>
-      <c r="L47">
         <v>2</v>
       </c>
-      <c r="M47" s="1" t="str">
+      <c r="L47" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C47),E47)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>46</v>
       </c>
@@ -3369,18 +3456,18 @@
       <c r="I48" t="s">
         <v>22</v>
       </c>
+      <c r="J48">
+        <v>11</v>
+      </c>
       <c r="K48">
-        <v>11</v>
-      </c>
-      <c r="L48">
         <v>1</v>
       </c>
-      <c r="M48" s="1" t="str">
+      <c r="L48" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C48),E48)</f>
         <v>Firemove LTD 130</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>47</v>
       </c>
@@ -3405,18 +3492,18 @@
       <c r="I49" t="s">
         <v>43</v>
       </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
       <c r="K49">
         <v>2</v>
       </c>
-      <c r="L49">
-        <v>2</v>
-      </c>
-      <c r="M49" s="1" t="str">
+      <c r="L49" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C49),E49)</f>
         <v>firerace</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>48</v>
       </c>
@@ -3441,18 +3528,18 @@
       <c r="I50" t="s">
         <v>58</v>
       </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
       <c r="K50">
-        <v>4</v>
-      </c>
-      <c r="L50">
         <v>1</v>
       </c>
-      <c r="M50" s="1" t="str">
+      <c r="L50" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C50),E50)</f>
         <v>Firerace W-tech 102</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>49</v>
       </c>
@@ -3477,18 +3564,18 @@
       <c r="I51" t="s">
         <v>43</v>
       </c>
+      <c r="J51">
+        <v>10</v>
+      </c>
       <c r="K51">
-        <v>10</v>
-      </c>
-      <c r="L51">
         <v>1</v>
       </c>
-      <c r="M51" s="1" t="str">
+      <c r="L51" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C51),E51)</f>
         <v>Firerace W-tech 112</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>50</v>
       </c>
@@ -3513,18 +3600,18 @@
       <c r="I52" t="s">
         <v>58</v>
       </c>
+      <c r="J52">
+        <v>26</v>
+      </c>
       <c r="K52">
-        <v>26</v>
-      </c>
-      <c r="L52">
         <v>1</v>
       </c>
-      <c r="M52" s="1" t="str">
+      <c r="L52" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C52),E52)</f>
         <v>Firestorm 120 W-tech</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>51</v>
       </c>
@@ -3549,15 +3636,15 @@
       <c r="I53" t="s">
         <v>26</v>
       </c>
-      <c r="K53">
+      <c r="J53">
         <v>1</v>
       </c>
-      <c r="M53" s="1" t="str">
+      <c r="L53" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C53),E53)</f>
         <v>FireWave 102 LTD</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54">
         <v>52</v>
@@ -3583,18 +3670,18 @@
       <c r="I54" t="s">
         <v>26</v>
       </c>
+      <c r="J54">
+        <v>29</v>
+      </c>
       <c r="K54">
-        <v>29</v>
-      </c>
-      <c r="L54">
         <v>1</v>
       </c>
-      <c r="M54" s="1" t="str">
+      <c r="L54" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C54),E54)</f>
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>53</v>
       </c>
@@ -3619,18 +3706,18 @@
       <c r="I55" t="s">
         <v>26</v>
       </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
       <c r="K55">
         <v>4</v>
       </c>
-      <c r="L55">
-        <v>4</v>
-      </c>
-      <c r="M55" s="1" t="str">
+      <c r="L55" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C55),E55)</f>
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>54</v>
       </c>
@@ -3655,18 +3742,18 @@
       <c r="I56" t="s">
         <v>26</v>
       </c>
+      <c r="J56">
+        <v>19</v>
+      </c>
       <c r="K56">
-        <v>19</v>
-      </c>
-      <c r="L56">
         <v>1</v>
       </c>
-      <c r="M56" s="1" t="str">
+      <c r="L56" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C56),E56)</f>
         <v>Freestyle Wave LTD</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>55</v>
       </c>
@@ -3691,15 +3778,15 @@
       <c r="I57" t="s">
         <v>26</v>
       </c>
-      <c r="K57">
+      <c r="J57">
         <v>2</v>
       </c>
-      <c r="M57" s="1" t="str">
+      <c r="L57" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C57),E57)</f>
         <v>FreeStyleWave</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>56</v>
       </c>
@@ -3724,18 +3811,18 @@
       <c r="I58" t="s">
         <v>26</v>
       </c>
+      <c r="J58">
+        <v>19</v>
+      </c>
       <c r="K58">
-        <v>19</v>
-      </c>
-      <c r="L58">
         <v>2</v>
       </c>
-      <c r="M58" s="1" t="str">
+      <c r="L58" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C58),E58)</f>
         <v>Frrestyle Wave 102</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>57</v>
       </c>
@@ -3760,12 +3847,12 @@
       <c r="I59" t="s">
         <v>58</v>
       </c>
-      <c r="M59" s="1" t="str">
+      <c r="L59" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C59),E59)</f>
         <v>Slalom</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>58</v>
       </c>
@@ -3790,18 +3877,18 @@
       <c r="I60" t="s">
         <v>61</v>
       </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
       <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60">
         <v>2</v>
       </c>
-      <c r="M60" s="1" t="str">
+      <c r="L60" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C60),E60)</f>
         <v>Slalom/speed</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>59</v>
       </c>
@@ -3826,18 +3913,18 @@
       <c r="I61" t="s">
         <v>61</v>
       </c>
+      <c r="J61">
+        <v>6</v>
+      </c>
       <c r="K61">
-        <v>6</v>
-      </c>
-      <c r="L61">
         <v>1</v>
       </c>
-      <c r="M61" s="1" t="str">
+      <c r="L61" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C61),E61)</f>
         <v>X-fire LTD V5</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>60</v>
       </c>
@@ -3862,18 +3949,18 @@
       <c r="I62" t="s">
         <v>58</v>
       </c>
+      <c r="J62">
+        <v>309</v>
+      </c>
       <c r="K62">
-        <v>309</v>
-      </c>
-      <c r="L62">
         <v>11</v>
       </c>
-      <c r="M62" s="1" t="str">
+      <c r="L62" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C62),E62)</f>
         <v>X-Fire LTD V5 105</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>61</v>
       </c>
@@ -3898,18 +3985,18 @@
       <c r="I63" t="s">
         <v>58</v>
       </c>
+      <c r="J63">
+        <v>417</v>
+      </c>
       <c r="K63">
-        <v>417</v>
-      </c>
-      <c r="L63">
         <v>15</v>
       </c>
-      <c r="M63" s="1" t="str">
+      <c r="L63" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C63),E63)</f>
         <v>X-Fire LTD V5 114</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>62</v>
       </c>
@@ -3934,18 +4021,18 @@
       <c r="I64" t="s">
         <v>58</v>
       </c>
+      <c r="J64">
+        <v>45</v>
+      </c>
       <c r="K64">
-        <v>45</v>
-      </c>
-      <c r="L64">
         <v>9</v>
       </c>
-      <c r="M64" s="1" t="str">
+      <c r="L64" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C64),E64)</f>
         <v>X-Fire LTD V5 114 2013</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>63</v>
       </c>
@@ -3970,18 +4057,18 @@
       <c r="I65" t="s">
         <v>22</v>
       </c>
+      <c r="J65">
+        <v>242</v>
+      </c>
       <c r="K65">
-        <v>242</v>
-      </c>
-      <c r="L65">
-        <v>10</v>
-      </c>
-      <c r="M65" s="1" t="str">
+        <v>10</v>
+      </c>
+      <c r="L65" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C65),E65)</f>
         <v>X-Fire LTD V5 122</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>64</v>
       </c>
@@ -4006,18 +4093,18 @@
       <c r="I66" t="s">
         <v>22</v>
       </c>
+      <c r="J66">
+        <v>214</v>
+      </c>
       <c r="K66">
-        <v>214</v>
-      </c>
-      <c r="L66">
         <v>14</v>
       </c>
-      <c r="M66" s="1" t="str">
+      <c r="L66" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C66),E66)</f>
         <v>X-Fire LTD V5 129</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>65</v>
       </c>
@@ -4042,18 +4129,18 @@
       <c r="I67" t="s">
         <v>61</v>
       </c>
+      <c r="J67">
+        <v>123</v>
+      </c>
       <c r="K67">
-        <v>123</v>
-      </c>
-      <c r="L67">
         <v>7</v>
       </c>
-      <c r="M67" s="1" t="str">
+      <c r="L67" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C67),E67)</f>
         <v>X-Fire LTD V5 90</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>66</v>
       </c>
@@ -4078,18 +4165,18 @@
       <c r="I68" t="s">
         <v>58</v>
       </c>
+      <c r="J68">
+        <v>589</v>
+      </c>
       <c r="K68">
-        <v>589</v>
-      </c>
-      <c r="L68">
         <v>24</v>
       </c>
-      <c r="M68" s="1" t="str">
+      <c r="L68" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C68),E68)</f>
         <v>X-Fire LTD V5 98</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>67</v>
       </c>
@@ -4114,18 +4201,18 @@
       <c r="I69" t="s">
         <v>14</v>
       </c>
+      <c r="J69">
+        <v>9</v>
+      </c>
       <c r="K69">
-        <v>9</v>
-      </c>
-      <c r="L69">
         <v>3</v>
       </c>
-      <c r="M69" s="1" t="str">
+      <c r="L69" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C69),E69)</f>
         <v>Custom Speed</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>68</v>
       </c>
@@ -4150,18 +4237,18 @@
       <c r="I70" t="s">
         <v>58</v>
       </c>
+      <c r="J70">
+        <v>23</v>
+      </c>
       <c r="K70">
-        <v>23</v>
-      </c>
-      <c r="L70">
         <v>2</v>
       </c>
-      <c r="M70" s="1" t="str">
+      <c r="L70" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C70),E70)</f>
         <v>Fire Storm 111</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>69</v>
       </c>
@@ -4186,18 +4273,18 @@
       <c r="I71" t="s">
         <v>58</v>
       </c>
+      <c r="J71">
+        <v>23</v>
+      </c>
       <c r="K71">
-        <v>23</v>
-      </c>
-      <c r="L71">
         <v>3</v>
       </c>
-      <c r="M71" s="1" t="str">
+      <c r="L71" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C71),E71)</f>
         <v>Fire Storm 138 W-Tech</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>70</v>
       </c>
@@ -4222,18 +4309,18 @@
       <c r="I72" t="s">
         <v>58</v>
       </c>
+      <c r="J72">
+        <v>13</v>
+      </c>
       <c r="K72">
-        <v>13</v>
-      </c>
-      <c r="L72">
         <v>3</v>
       </c>
-      <c r="M72" s="1" t="str">
+      <c r="L72" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C72),E72)</f>
         <v>Fire Strom LTD</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>71</v>
       </c>
@@ -4258,18 +4345,18 @@
       <c r="I73" t="s">
         <v>26</v>
       </c>
+      <c r="J73">
+        <v>6</v>
+      </c>
       <c r="K73">
-        <v>6</v>
-      </c>
-      <c r="L73">
         <v>1</v>
       </c>
-      <c r="M73" s="1" t="str">
+      <c r="L73" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C73),E73)</f>
         <v>firemove 100</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>72</v>
       </c>
@@ -4294,18 +4381,18 @@
       <c r="I74" t="s">
         <v>58</v>
       </c>
+      <c r="J74">
+        <v>22</v>
+      </c>
       <c r="K74">
-        <v>22</v>
-      </c>
-      <c r="L74">
         <v>2</v>
       </c>
-      <c r="M74" s="1" t="str">
+      <c r="L74" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C74),E74)</f>
         <v>FireMove 100 X-Tech</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>73</v>
       </c>
@@ -4330,18 +4417,18 @@
       <c r="I75" t="s">
         <v>26</v>
       </c>
+      <c r="J75">
+        <v>5</v>
+      </c>
       <c r="K75">
-        <v>5</v>
-      </c>
-      <c r="L75">
         <v>1</v>
       </c>
-      <c r="M75" s="1" t="str">
+      <c r="L75" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C75),E75)</f>
         <v>firemove 110</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>74</v>
       </c>
@@ -4366,18 +4453,18 @@
       <c r="I76" t="s">
         <v>26</v>
       </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
       <c r="K76">
-        <v>2</v>
-      </c>
-      <c r="L76">
         <v>1</v>
       </c>
-      <c r="M76" s="1" t="str">
+      <c r="L76" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C76),E76)</f>
         <v>FireMove 110 X-Tech</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>75</v>
       </c>
@@ -4402,18 +4489,18 @@
       <c r="I77" t="s">
         <v>22</v>
       </c>
+      <c r="J77">
+        <v>25</v>
+      </c>
       <c r="K77">
-        <v>25</v>
-      </c>
-      <c r="L77">
         <v>1</v>
       </c>
-      <c r="M77" s="1" t="str">
+      <c r="L77" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C77),E77)</f>
         <v>Firemove 120</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>76</v>
       </c>
@@ -4438,18 +4525,18 @@
       <c r="I78" t="s">
         <v>159</v>
       </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
       <c r="K78">
         <v>1</v>
       </c>
-      <c r="L78">
-        <v>1</v>
-      </c>
-      <c r="M78" s="1" t="str">
+      <c r="L78" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C78),E78)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>77</v>
       </c>
@@ -4474,18 +4561,18 @@
       <c r="I79" t="s">
         <v>159</v>
       </c>
+      <c r="J79">
+        <v>31</v>
+      </c>
       <c r="K79">
-        <v>31</v>
-      </c>
-      <c r="L79">
         <v>1</v>
       </c>
-      <c r="M79" s="1" t="str">
+      <c r="L79" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C79),E79)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>78</v>
       </c>
@@ -4510,18 +4597,18 @@
       <c r="I80" t="s">
         <v>43</v>
       </c>
+      <c r="J80">
+        <v>4</v>
+      </c>
       <c r="K80">
-        <v>4</v>
-      </c>
-      <c r="L80">
         <v>2</v>
       </c>
-      <c r="M80" s="1" t="str">
+      <c r="L80" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C80),E80)</f>
         <v>Firemove LTD</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>79</v>
       </c>
@@ -4546,18 +4633,18 @@
       <c r="I81" t="s">
         <v>43</v>
       </c>
+      <c r="J81">
+        <v>83</v>
+      </c>
       <c r="K81">
-        <v>83</v>
-      </c>
-      <c r="L81">
         <v>4</v>
       </c>
-      <c r="M81" s="1" t="str">
+      <c r="L81" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C81),E81)</f>
         <v>Firemove LTD 100</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>80</v>
       </c>
@@ -4582,18 +4669,18 @@
       <c r="I82" t="s">
         <v>58</v>
       </c>
+      <c r="J82">
+        <v>130</v>
+      </c>
       <c r="K82">
-        <v>130</v>
-      </c>
-      <c r="L82">
         <v>6</v>
       </c>
-      <c r="M82" s="1" t="str">
+      <c r="L82" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C82),E82)</f>
         <v>Firemove LTD 110</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>81</v>
       </c>
@@ -4618,18 +4705,18 @@
       <c r="I83" t="s">
         <v>22</v>
       </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
       <c r="K83">
         <v>1</v>
       </c>
-      <c r="L83">
-        <v>1</v>
-      </c>
-      <c r="M83" s="1" t="str">
+      <c r="L83" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C83),E83)</f>
         <v>Firerace V3 122</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>82</v>
       </c>
@@ -4654,18 +4741,18 @@
       <c r="I84" t="s">
         <v>58</v>
       </c>
+      <c r="J84">
+        <v>73</v>
+      </c>
       <c r="K84">
-        <v>73</v>
-      </c>
-      <c r="L84">
         <v>3</v>
       </c>
-      <c r="M84" s="1" t="str">
+      <c r="L84" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C84),E84)</f>
         <v>Firestorm</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>83</v>
       </c>
@@ -4690,18 +4777,18 @@
       <c r="I85" t="s">
         <v>26</v>
       </c>
+      <c r="J85">
+        <v>3</v>
+      </c>
       <c r="K85">
-        <v>3</v>
-      </c>
-      <c r="L85">
         <v>1</v>
       </c>
-      <c r="M85" s="1" t="str">
+      <c r="L85" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C85),E85)</f>
         <v>Freestyle Wave</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>84</v>
       </c>
@@ -4726,18 +4813,18 @@
       <c r="I86" t="s">
         <v>26</v>
       </c>
+      <c r="J86">
+        <v>4</v>
+      </c>
       <c r="K86">
-        <v>4</v>
-      </c>
-      <c r="L86">
         <v>1</v>
       </c>
-      <c r="M86" s="1" t="str">
+      <c r="L86" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C86),E86)</f>
         <v>Freestyle Wave 90 X-Tech</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>85</v>
       </c>
@@ -4762,18 +4849,18 @@
       <c r="I87" t="s">
         <v>26</v>
       </c>
+      <c r="J87">
+        <v>33</v>
+      </c>
       <c r="K87">
-        <v>33</v>
-      </c>
-      <c r="L87">
         <v>1</v>
       </c>
-      <c r="M87" s="1" t="str">
+      <c r="L87" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C87),E87)</f>
         <v>Freestyle Wave 96 LTD</v>
       </c>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>86</v>
       </c>
@@ -4798,18 +4885,18 @@
       <c r="I88" t="s">
         <v>26</v>
       </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
       <c r="K88">
         <v>1</v>
       </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88" s="1" t="str">
+      <c r="L88" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C88),E88)</f>
         <v>FreestyleWave</v>
       </c>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>87</v>
       </c>
@@ -4834,18 +4921,18 @@
       <c r="I89" t="s">
         <v>26</v>
       </c>
+      <c r="J89">
+        <v>6</v>
+      </c>
       <c r="K89">
-        <v>6</v>
-      </c>
-      <c r="L89">
         <v>3</v>
       </c>
-      <c r="M89" s="1" t="str">
+      <c r="L89" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C89),E89)</f>
         <v>TwinTip LTD</v>
       </c>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>88</v>
       </c>
@@ -4870,18 +4957,18 @@
       <c r="I90" t="s">
         <v>43</v>
       </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
       <c r="K90">
         <v>1</v>
       </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
-      <c r="M90" s="1" t="str">
+      <c r="L90" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C90),E90)</f>
         <v>wave cult</v>
       </c>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>89</v>
       </c>
@@ -4906,12 +4993,12 @@
       <c r="I91" t="s">
         <v>58</v>
       </c>
-      <c r="M91" s="1" t="str">
+      <c r="L91" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C91),E91)</f>
         <v>X-fire</v>
       </c>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>90</v>
       </c>
@@ -4936,15 +5023,15 @@
       <c r="I92" t="s">
         <v>61</v>
       </c>
-      <c r="K92">
+      <c r="J92">
         <v>1</v>
       </c>
-      <c r="M92" s="1" t="str">
+      <c r="L92" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C92),E92)</f>
         <v>xfire 105</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>91</v>
       </c>
@@ -4969,18 +5056,18 @@
       <c r="I93" t="s">
         <v>182</v>
       </c>
+      <c r="J93">
+        <v>16</v>
+      </c>
       <c r="K93">
-        <v>16</v>
-      </c>
-      <c r="L93">
         <v>3</v>
       </c>
-      <c r="M93" s="1" t="str">
+      <c r="L93" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C93),E93)</f>
         <v>X-Fire 80 V</v>
       </c>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>92</v>
       </c>
@@ -5005,15 +5092,15 @@
       <c r="I94" t="s">
         <v>58</v>
       </c>
-      <c r="K94">
+      <c r="J94">
         <v>5</v>
       </c>
-      <c r="M94" s="1" t="str">
+      <c r="L94" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C94),E94)</f>
         <v>X-Fire LTD 105</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>93</v>
       </c>
@@ -5038,18 +5125,18 @@
       <c r="I95" t="s">
         <v>22</v>
       </c>
+      <c r="J95">
+        <v>45</v>
+      </c>
       <c r="K95">
-        <v>45</v>
-      </c>
-      <c r="L95">
         <v>8</v>
       </c>
-      <c r="M95" s="1" t="str">
+      <c r="L95" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C95),E95)</f>
         <v>X-Fire Ltd V3 122</v>
       </c>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>94</v>
       </c>
@@ -5074,18 +5161,18 @@
       <c r="I96" t="s">
         <v>58</v>
       </c>
+      <c r="J96">
+        <v>29</v>
+      </c>
       <c r="K96">
-        <v>29</v>
-      </c>
-      <c r="L96">
         <v>3</v>
       </c>
-      <c r="M96" s="1" t="str">
+      <c r="L96" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C96),E96)</f>
         <v>X-Fire LTD V4</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>95</v>
       </c>
@@ -5110,18 +5197,18 @@
       <c r="I97" t="s">
         <v>58</v>
       </c>
+      <c r="J97">
+        <v>135</v>
+      </c>
       <c r="K97">
-        <v>135</v>
-      </c>
-      <c r="L97">
         <v>5</v>
       </c>
-      <c r="M97" s="1" t="str">
+      <c r="L97" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C97),E97)</f>
         <v>X-Fire LTD V4 105</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>96</v>
       </c>
@@ -5146,18 +5233,18 @@
       <c r="I98" t="s">
         <v>58</v>
       </c>
+      <c r="J98">
+        <v>431</v>
+      </c>
       <c r="K98">
-        <v>431</v>
-      </c>
-      <c r="L98">
         <v>22</v>
       </c>
-      <c r="M98" s="1" t="str">
+      <c r="L98" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C98),E98)</f>
         <v>X-Fire LTD V4 114</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>97</v>
       </c>
@@ -5182,18 +5269,18 @@
       <c r="I99" t="s">
         <v>22</v>
       </c>
+      <c r="J99">
+        <v>373</v>
+      </c>
       <c r="K99">
-        <v>373</v>
-      </c>
-      <c r="L99">
         <v>11</v>
       </c>
-      <c r="M99" s="1" t="str">
+      <c r="L99" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C99),E99)</f>
         <v>X-Fire LTD V4 122</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>98</v>
       </c>
@@ -5218,18 +5305,18 @@
       <c r="I100" t="s">
         <v>67</v>
       </c>
+      <c r="J100">
+        <v>79</v>
+      </c>
       <c r="K100">
-        <v>79</v>
-      </c>
-      <c r="L100">
         <v>9</v>
       </c>
-      <c r="M100" s="1" t="str">
+      <c r="L100" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C100),E100)</f>
         <v>X-Fire LTD V4 129</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>99</v>
       </c>
@@ -5254,18 +5341,18 @@
       <c r="I101" t="s">
         <v>61</v>
       </c>
+      <c r="J101">
+        <v>121</v>
+      </c>
       <c r="K101">
-        <v>121</v>
-      </c>
-      <c r="L101">
         <v>8</v>
       </c>
-      <c r="M101" s="1" t="str">
+      <c r="L101" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C101),E101)</f>
         <v>X-Fire LTD V4 90</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>100</v>
       </c>
@@ -5290,18 +5377,18 @@
       <c r="I102" t="s">
         <v>58</v>
       </c>
+      <c r="J102">
+        <v>282</v>
+      </c>
       <c r="K102">
-        <v>282</v>
-      </c>
-      <c r="L102">
         <v>15</v>
       </c>
-      <c r="M102" s="1" t="str">
+      <c r="L102" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C102),E102)</f>
         <v>X-Fire LTD V4 98</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>101</v>
       </c>
@@ -5326,18 +5413,18 @@
       <c r="I103" t="s">
         <v>58</v>
       </c>
+      <c r="J103">
+        <v>106</v>
+      </c>
       <c r="K103">
-        <v>106</v>
-      </c>
-      <c r="L103">
         <v>8</v>
       </c>
-      <c r="M103" s="1" t="str">
+      <c r="L103" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C103),E103)</f>
         <v>X-FIRE V3</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>102</v>
       </c>
@@ -5362,18 +5449,18 @@
       <c r="I104" t="s">
         <v>58</v>
       </c>
+      <c r="J104">
+        <v>6</v>
+      </c>
       <c r="K104">
-        <v>6</v>
-      </c>
-      <c r="L104">
         <v>1</v>
       </c>
-      <c r="M104" s="1" t="str">
+      <c r="L104" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C104),E104)</f>
         <v>X-Fire V4</v>
       </c>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>103</v>
       </c>
@@ -5399,17 +5486,14 @@
         <v>43</v>
       </c>
       <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
         <v>13</v>
       </c>
-      <c r="M105" s="1" t="str">
+      <c r="L105" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C105),E105)</f>
         <v>Atom IQ</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>104</v>
       </c>
@@ -5435,20 +5519,17 @@
         <v>58</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K106">
-        <v>7</v>
-      </c>
-      <c r="L106">
         <v>1</v>
       </c>
-      <c r="M106" s="1" t="str">
+      <c r="L106" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C106),E106)</f>
         <v>Atom IQ 100 Tufskin</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>105</v>
       </c>
@@ -5474,20 +5555,17 @@
         <v>43</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K107">
-        <v>15</v>
-      </c>
-      <c r="L107">
         <v>4</v>
       </c>
-      <c r="M107" s="1" t="str">
+      <c r="L107" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C107),E107)</f>
         <v>Atom IQ carbon 110</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>106</v>
       </c>
@@ -5513,20 +5591,17 @@
         <v>22</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="K108">
-        <v>79</v>
-      </c>
-      <c r="L108">
         <v>6</v>
       </c>
-      <c r="M108" s="1" t="str">
+      <c r="L108" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C108),E108)</f>
         <v>AtomIQ 120 Carbon</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>107</v>
       </c>
@@ -5552,20 +5627,17 @@
         <v>58</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109">
         <v>1</v>
       </c>
-      <c r="L109">
-        <v>1</v>
-      </c>
-      <c r="M109" s="1" t="str">
+      <c r="L109" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C109),E109)</f>
         <v>Carve 111 wood</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>108</v>
       </c>
@@ -5591,20 +5663,17 @@
         <v>227</v>
       </c>
       <c r="J110">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="K110">
-        <v>60</v>
-      </c>
-      <c r="L110">
         <v>2</v>
       </c>
-      <c r="M110" s="1" t="str">
+      <c r="L110" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C110),E110)</f>
         <v>Fórmula 167 blue</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>109</v>
       </c>
@@ -5630,20 +5699,17 @@
         <v>58</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K111">
-        <v>4</v>
-      </c>
-      <c r="L111">
         <v>3</v>
       </c>
-      <c r="M111" s="1" t="str">
+      <c r="L111" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C111),E111)</f>
         <v>Futura</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>110</v>
       </c>
@@ -5669,20 +5735,17 @@
         <v>43</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K112">
-        <v>57</v>
-      </c>
-      <c r="L112">
         <v>2</v>
       </c>
-      <c r="M112" s="1" t="str">
+      <c r="L112" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C112),E112)</f>
         <v>Futura 104 carbon</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>111</v>
       </c>
@@ -5708,20 +5771,17 @@
         <v>58</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="K113">
-        <v>57</v>
-      </c>
-      <c r="L113">
         <v>2</v>
       </c>
-      <c r="M113" s="1" t="str">
+      <c r="L113" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C113),E113)</f>
         <v>Futura 104 wood</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>112</v>
       </c>
@@ -5747,20 +5807,17 @@
         <v>43</v>
       </c>
       <c r="J114">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K114">
-        <v>55</v>
-      </c>
-      <c r="L114">
         <v>2</v>
       </c>
-      <c r="M114" s="1" t="str">
+      <c r="L114" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C114),E114)</f>
         <v>Futura 114 carbon</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>113</v>
       </c>
@@ -5786,20 +5843,17 @@
         <v>58</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K115">
-        <v>70</v>
-      </c>
-      <c r="L115">
         <v>8</v>
       </c>
-      <c r="M115" s="1" t="str">
+      <c r="L115" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C115),E115)</f>
         <v>Futura 114 wood</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>114</v>
       </c>
@@ -5825,20 +5879,17 @@
         <v>58</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K116">
-        <v>21</v>
-      </c>
-      <c r="L116">
         <v>4</v>
       </c>
-      <c r="M116" s="1" t="str">
+      <c r="L116" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C116),E116)</f>
         <v>Futura 124 Carbon</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>115</v>
       </c>
@@ -5864,20 +5915,17 @@
         <v>22</v>
       </c>
       <c r="J117">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K117">
-        <v>221</v>
-      </c>
-      <c r="L117">
         <v>5</v>
       </c>
-      <c r="M117" s="1" t="str">
+      <c r="L117" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C117),E117)</f>
         <v>Futura 124 Wood</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>116</v>
       </c>
@@ -5903,20 +5951,17 @@
         <v>58</v>
       </c>
       <c r="J118">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K118">
-        <v>12</v>
-      </c>
-      <c r="L118">
         <v>1</v>
       </c>
-      <c r="M118" s="1" t="str">
+      <c r="L118" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C118),E118)</f>
         <v>Futura 133 Wood</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>117</v>
       </c>
@@ -5942,20 +5987,17 @@
         <v>22</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K119">
-        <v>74</v>
-      </c>
-      <c r="L119">
         <v>3</v>
       </c>
-      <c r="M119" s="1" t="str">
+      <c r="L119" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C119),E119)</f>
         <v>Futura 134 Carbon</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>118</v>
       </c>
@@ -5981,20 +6023,17 @@
         <v>22</v>
       </c>
       <c r="J120">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K120">
-        <v>48</v>
-      </c>
-      <c r="L120">
         <v>5</v>
       </c>
-      <c r="M120" s="1" t="str">
+      <c r="L120" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C120),E120)</f>
         <v>Futura 134 Wood</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>119</v>
       </c>
@@ -6020,20 +6059,17 @@
         <v>43</v>
       </c>
       <c r="J121">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K121">
-        <v>6</v>
-      </c>
-      <c r="L121">
         <v>3</v>
       </c>
-      <c r="M121" s="1" t="str">
+      <c r="L121" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C121),E121)</f>
         <v>Futura 90 Wood</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>120</v>
       </c>
@@ -6059,20 +6095,17 @@
         <v>58</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K122">
-        <v>17</v>
-      </c>
-      <c r="L122">
         <v>1</v>
       </c>
-      <c r="M122" s="1" t="str">
+      <c r="L122" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C122),E122)</f>
         <v>Futura 93 wood</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>121</v>
       </c>
@@ -6098,20 +6131,17 @@
         <v>43</v>
       </c>
       <c r="J123">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K123">
-        <v>36</v>
-      </c>
-      <c r="L123">
         <v>1</v>
       </c>
-      <c r="M123" s="1" t="str">
+      <c r="L123" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C123),E123)</f>
         <v>Futura 97 wood</v>
       </c>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>122</v>
       </c>
@@ -6137,20 +6167,17 @@
         <v>58</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K124">
-        <v>14</v>
-      </c>
-      <c r="L124">
         <v>1</v>
       </c>
-      <c r="M124" s="1" t="str">
+      <c r="L124" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C124),E124)</f>
         <v>Futura carbon</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>123</v>
       </c>
@@ -6176,17 +6203,14 @@
         <v>58</v>
       </c>
       <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
         <v>2</v>
       </c>
-      <c r="M125" s="1" t="str">
+      <c r="L125" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C125),E125)</f>
         <v>Futura Carbon</v>
       </c>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>124</v>
       </c>
@@ -6212,20 +6236,17 @@
         <v>22</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K126">
-        <v>10</v>
-      </c>
-      <c r="L126">
         <v>2</v>
       </c>
-      <c r="M126" s="1" t="str">
+      <c r="L126" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C126),E126)</f>
         <v>Go 139 Tufskin</v>
       </c>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>125</v>
       </c>
@@ -6251,20 +6272,17 @@
         <v>58</v>
       </c>
       <c r="J127">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K127">
-        <v>39</v>
-      </c>
-      <c r="L127">
         <v>6</v>
       </c>
-      <c r="M127" s="1" t="str">
+      <c r="L127" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C127),E127)</f>
         <v>Isonic</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>126</v>
       </c>
@@ -6290,20 +6308,17 @@
         <v>58</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="K128">
-        <v>1388</v>
-      </c>
-      <c r="L128">
         <v>56</v>
       </c>
-      <c r="M128" s="1" t="str">
+      <c r="L128" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C128),E128)</f>
         <v>iSonic 107 Carbon</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>127</v>
       </c>
@@ -6329,20 +6344,17 @@
         <v>58</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K129">
-        <v>12</v>
-      </c>
-      <c r="L129">
         <v>1</v>
       </c>
-      <c r="M129" s="1" t="str">
+      <c r="L129" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C129),E129)</f>
         <v>iSonic 107 wood</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>128</v>
       </c>
@@ -6368,20 +6380,17 @@
         <v>22</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="K130">
-        <v>149</v>
-      </c>
-      <c r="L130">
         <v>17</v>
       </c>
-      <c r="M130" s="1" t="str">
+      <c r="L130" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C130),E130)</f>
         <v>iSonic 110 Carbon</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>129</v>
       </c>
@@ -6407,20 +6416,17 @@
         <v>22</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K131">
-        <v>44</v>
-      </c>
-      <c r="L131">
         <v>4</v>
       </c>
-      <c r="M131" s="1" t="str">
+      <c r="L131" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C131),E131)</f>
         <v>Isonic 117</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>130</v>
       </c>
@@ -6446,20 +6452,17 @@
         <v>22</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K132">
-        <v>40</v>
-      </c>
-      <c r="L132">
         <v>1</v>
       </c>
-      <c r="M132" s="1" t="str">
+      <c r="L132" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C132),E132)</f>
         <v>iSonic 117 wood</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>131</v>
       </c>
@@ -6485,20 +6488,17 @@
         <v>22</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="K133">
-        <v>541</v>
-      </c>
-      <c r="L133">
         <v>18</v>
       </c>
-      <c r="M133" s="1" t="str">
+      <c r="L133" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C133),E133)</f>
         <v>Isonic 120 carbon</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>132</v>
       </c>
@@ -6524,20 +6524,17 @@
         <v>67</v>
       </c>
       <c r="J134">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="K134">
-        <v>480</v>
-      </c>
-      <c r="L134">
         <v>18</v>
       </c>
-      <c r="M134" s="1" t="str">
+      <c r="L134" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C134),E134)</f>
         <v>iSonic 130 Carbon</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>133</v>
       </c>
@@ -6563,20 +6560,17 @@
         <v>61</v>
       </c>
       <c r="J135">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K135">
-        <v>60</v>
-      </c>
-      <c r="L135">
         <v>2</v>
       </c>
-      <c r="M135" s="1" t="str">
+      <c r="L135" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C135),E135)</f>
         <v>Isonic 80 Wood</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>134</v>
       </c>
@@ -6602,20 +6596,17 @@
         <v>61</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="K136">
-        <v>502</v>
-      </c>
-      <c r="L136">
         <v>23</v>
       </c>
-      <c r="M136" s="1" t="str">
+      <c r="L136" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C136),E136)</f>
         <v>isonic 87 Carbon</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>135</v>
       </c>
@@ -6641,20 +6632,17 @@
         <v>61</v>
       </c>
       <c r="J137">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K137">
-        <v>45</v>
-      </c>
-      <c r="L137">
         <v>3</v>
       </c>
-      <c r="M137" s="1" t="str">
+      <c r="L137" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C137),E137)</f>
         <v>iSonic 87 wood</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>136</v>
       </c>
@@ -6680,20 +6668,17 @@
         <v>61</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>429</v>
       </c>
       <c r="K138">
-        <v>429</v>
-      </c>
-      <c r="L138">
         <v>27</v>
       </c>
-      <c r="M138" s="1" t="str">
+      <c r="L138" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C138),E138)</f>
         <v>Isonic 90 Carbon</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>137</v>
       </c>
@@ -6719,20 +6704,17 @@
         <v>58</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="K139">
-        <v>436</v>
-      </c>
-      <c r="L139">
         <v>22</v>
       </c>
-      <c r="M139" s="1" t="str">
+      <c r="L139" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C139),E139)</f>
         <v>iSonic 97 Carbon</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>138</v>
       </c>
@@ -6758,20 +6740,17 @@
         <v>58</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="K140">
-        <v>42</v>
-      </c>
-      <c r="L140">
         <v>1</v>
       </c>
-      <c r="M140" s="1" t="str">
+      <c r="L140" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C140),E140)</f>
         <v>Isonic 97 wood</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>139</v>
       </c>
@@ -6797,22 +6776,19 @@
         <v>22</v>
       </c>
       <c r="J141">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K141">
-        <v>25</v>
-      </c>
-      <c r="L141">
         <v>4</v>
       </c>
-      <c r="M141" s="1" t="str">
+      <c r="L141" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C141),E141)</f>
         <v>Isonic carbon</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B142">
         <v>140</v>
@@ -6839,20 +6815,17 @@
         <v>14</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="K142">
-        <v>216</v>
-      </c>
-      <c r="L142">
         <v>4</v>
       </c>
-      <c r="M142" s="1" t="str">
+      <c r="L142" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C142),E142)</f>
         <v>I-Sonic Speed 54</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>141</v>
       </c>
@@ -6878,20 +6851,17 @@
         <v>14</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="K143">
-        <v>49</v>
-      </c>
-      <c r="L143">
         <v>8</v>
       </c>
-      <c r="M143" s="1" t="str">
+      <c r="L143" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C143),E143)</f>
         <v>iSonic speed special w44</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>142</v>
       </c>
@@ -6917,20 +6887,17 @@
         <v>14</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K144">
-        <v>43</v>
-      </c>
-      <c r="L144">
         <v>9</v>
       </c>
-      <c r="M144" s="1" t="str">
+      <c r="L144" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C144),E144)</f>
         <v>Isonic speed special W49</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>143</v>
       </c>
@@ -6956,20 +6923,17 @@
         <v>43</v>
       </c>
       <c r="J145">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="K145">
-        <v>206</v>
-      </c>
-      <c r="L145">
         <v>7</v>
       </c>
-      <c r="M145" s="1" t="str">
+      <c r="L145" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C145),E145)</f>
         <v>iSonic Speed Special W54</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>144</v>
       </c>
@@ -6995,17 +6959,14 @@
         <v>22</v>
       </c>
       <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
         <v>2</v>
       </c>
-      <c r="M146" s="1" t="str">
+      <c r="L146" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C146),E146)</f>
         <v>iSonics carbon</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>145</v>
       </c>
@@ -7031,17 +6992,14 @@
         <v>26</v>
       </c>
       <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
         <v>4</v>
       </c>
-      <c r="M147" s="1" t="str">
+      <c r="L147" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C147),E147)</f>
         <v>Kode 87 Wood Carbon</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>146</v>
       </c>
@@ -7067,20 +7025,17 @@
         <v>26</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K148">
-        <v>19</v>
-      </c>
-      <c r="L148">
         <v>4</v>
       </c>
-      <c r="M148" s="1" t="str">
+      <c r="L148" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C148),E148)</f>
         <v>Kode FreeWave Wood</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>147</v>
       </c>
@@ -7105,15 +7060,12 @@
       <c r="I149" t="s">
         <v>22</v>
       </c>
-      <c r="J149">
-        <v>3</v>
-      </c>
-      <c r="M149" s="1" t="str">
+      <c r="L149" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C149),E149)</f>
         <v>No idea</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>148</v>
       </c>
@@ -7139,20 +7091,17 @@
         <v>22</v>
       </c>
       <c r="J150">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K150">
-        <v>22</v>
-      </c>
-      <c r="L150">
         <v>4</v>
       </c>
-      <c r="M150" s="1" t="str">
+      <c r="L150" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C150),E150)</f>
         <v>Slalom One</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>149</v>
       </c>
@@ -7178,20 +7127,17 @@
         <v>14</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K151">
-        <v>14</v>
-      </c>
-      <c r="L151">
         <v>1</v>
       </c>
-      <c r="M151" s="1" t="str">
+      <c r="L151" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C151),E151)</f>
         <v>Speed special 58</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>150</v>
       </c>
@@ -7217,20 +7163,17 @@
         <v>67</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152">
         <v>2</v>
       </c>
-      <c r="L152">
-        <v>2</v>
-      </c>
-      <c r="M152" s="1" t="str">
+      <c r="L152" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C152),E152)</f>
         <v>Starboard AtomIQ 140</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>151</v>
       </c>
@@ -7256,20 +7199,17 @@
         <v>67</v>
       </c>
       <c r="J153">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K153">
-        <v>24</v>
-      </c>
-      <c r="L153">
         <v>2</v>
       </c>
-      <c r="M153" s="1" t="str">
+      <c r="L153" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C153),E153)</f>
         <v>Ultrasonic Wood</v>
       </c>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>152</v>
       </c>
@@ -7295,20 +7235,17 @@
         <v>316</v>
       </c>
       <c r="J154">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K154">
-        <v>4</v>
-      </c>
-      <c r="L154">
         <v>1</v>
       </c>
-      <c r="M154" s="1" t="str">
+      <c r="L154" s="1" t="str">
         <f>HYPERLINK(_xlfn.CONCAT($F$1,C154),E154)</f>
         <v>Windsup Touring Delux Inflatable</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>153</v>
       </c>
@@ -7319,13 +7256,13 @@
         <v>201</v>
       </c>
       <c r="E155" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F155" t="s">
         <v>166</v>
       </c>
       <c r="G155" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H155">
         <v>2007</v>
@@ -7333,18 +7270,18 @@
       <c r="I155" t="s">
         <v>26</v>
       </c>
+      <c r="J155">
+        <v>7</v>
+      </c>
       <c r="K155">
-        <v>7</v>
-      </c>
-      <c r="L155">
         <v>2</v>
       </c>
-      <c r="M155" s="1" t="str">
-        <f t="shared" ref="M155:M181" si="0">HYPERLINK(_xlfn.CONCAT($F$1,C155),E155)</f>
+      <c r="L155" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C155),E155)</f>
         <v>AllWave</v>
       </c>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>154</v>
       </c>
@@ -7355,13 +7292,13 @@
         <v>201</v>
       </c>
       <c r="E156" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F156" t="s">
         <v>105</v>
       </c>
       <c r="G156" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H156">
         <v>2007</v>
@@ -7369,15 +7306,15 @@
       <c r="I156" t="s">
         <v>43</v>
       </c>
-      <c r="K156">
+      <c r="J156">
         <v>3</v>
       </c>
-      <c r="M156" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L156" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C156),E156)</f>
         <v>Eagle</v>
       </c>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>155</v>
       </c>
@@ -7388,10 +7325,10 @@
         <v>201</v>
       </c>
       <c r="E157" t="s">
+        <v>325</v>
+      </c>
+      <c r="F157" t="s">
         <v>326</v>
-      </c>
-      <c r="F157" t="s">
-        <v>327</v>
       </c>
       <c r="G157" t="s">
         <v>117</v>
@@ -7402,18 +7339,18 @@
       <c r="I157" t="s">
         <v>58</v>
       </c>
+      <c r="J157">
+        <v>9</v>
+      </c>
       <c r="K157">
-        <v>9</v>
-      </c>
-      <c r="L157">
         <v>5</v>
       </c>
-      <c r="M157" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L157" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C157),E157)</f>
         <v>Eagle 100</v>
       </c>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>156</v>
       </c>
@@ -7424,13 +7361,13 @@
         <v>201</v>
       </c>
       <c r="E158" t="s">
+        <v>327</v>
+      </c>
+      <c r="F158" t="s">
         <v>328</v>
       </c>
-      <c r="F158" t="s">
-        <v>329</v>
-      </c>
       <c r="G158" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H158">
         <v>2007</v>
@@ -7438,18 +7375,18 @@
       <c r="I158" t="s">
         <v>58</v>
       </c>
+      <c r="J158">
+        <v>14</v>
+      </c>
       <c r="K158">
-        <v>14</v>
-      </c>
-      <c r="L158">
         <v>5</v>
       </c>
-      <c r="M158" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L158" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C158),E158)</f>
         <v>Eagle 126</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>157</v>
       </c>
@@ -7460,10 +7397,10 @@
         <v>201</v>
       </c>
       <c r="E159" t="s">
+        <v>329</v>
+      </c>
+      <c r="F159" t="s">
         <v>330</v>
-      </c>
-      <c r="F159" t="s">
-        <v>331</v>
       </c>
       <c r="G159" t="s">
         <v>89</v>
@@ -7474,18 +7411,18 @@
       <c r="I159" t="s">
         <v>58</v>
       </c>
+      <c r="J159">
+        <v>24</v>
+      </c>
       <c r="K159">
-        <v>24</v>
-      </c>
-      <c r="L159">
         <v>9</v>
       </c>
-      <c r="M159" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L159" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C159),E159)</f>
         <v>Falcon</v>
       </c>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>158</v>
       </c>
@@ -7496,10 +7433,10 @@
         <v>201</v>
       </c>
       <c r="E160" t="s">
+        <v>331</v>
+      </c>
+      <c r="F160" t="s">
         <v>332</v>
-      </c>
-      <c r="F160" t="s">
-        <v>333</v>
       </c>
       <c r="G160" t="s">
         <v>79</v>
@@ -7510,18 +7447,18 @@
       <c r="I160" t="s">
         <v>58</v>
       </c>
+      <c r="J160">
+        <v>832</v>
+      </c>
       <c r="K160">
-        <v>832</v>
-      </c>
-      <c r="L160">
         <v>30</v>
       </c>
-      <c r="M160" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L160" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C160),E160)</f>
         <v>Falcon 105</v>
       </c>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>159</v>
       </c>
@@ -7532,13 +7469,13 @@
         <v>201</v>
       </c>
       <c r="E161" t="s">
+        <v>333</v>
+      </c>
+      <c r="F161" t="s">
         <v>334</v>
       </c>
-      <c r="F161" t="s">
+      <c r="G161" t="s">
         <v>335</v>
-      </c>
-      <c r="G161" t="s">
-        <v>336</v>
       </c>
       <c r="H161">
         <v>2007</v>
@@ -7546,18 +7483,18 @@
       <c r="I161" t="s">
         <v>22</v>
       </c>
+      <c r="J161">
+        <v>961</v>
+      </c>
       <c r="K161">
-        <v>961</v>
-      </c>
-      <c r="L161">
         <v>27</v>
       </c>
-      <c r="M161" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L161" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C161),E161)</f>
         <v>Falcon 125</v>
       </c>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>160</v>
       </c>
@@ -7568,13 +7505,13 @@
         <v>201</v>
       </c>
       <c r="E162" t="s">
+        <v>336</v>
+      </c>
+      <c r="F162" t="s">
         <v>337</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>338</v>
-      </c>
-      <c r="G162" t="s">
-        <v>339</v>
       </c>
       <c r="H162">
         <v>2007</v>
@@ -7582,18 +7519,18 @@
       <c r="I162" t="s">
         <v>67</v>
       </c>
+      <c r="J162">
+        <v>33</v>
+      </c>
       <c r="K162">
-        <v>33</v>
-      </c>
-      <c r="L162">
         <v>5</v>
       </c>
-      <c r="M162" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L162" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C162),E162)</f>
         <v>Falcon 145</v>
       </c>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>161</v>
       </c>
@@ -7604,10 +7541,10 @@
         <v>201</v>
       </c>
       <c r="E163" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F163" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G163" t="s">
         <v>89</v>
@@ -7618,18 +7555,18 @@
       <c r="I163" t="s">
         <v>58</v>
       </c>
+      <c r="J163">
+        <v>2396</v>
+      </c>
       <c r="K163">
-        <v>2396</v>
-      </c>
-      <c r="L163">
         <v>61</v>
       </c>
-      <c r="M163" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L163" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C163),E163)</f>
         <v>Falcon 90</v>
       </c>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>162</v>
       </c>
@@ -7640,10 +7577,10 @@
         <v>201</v>
       </c>
       <c r="E164" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F164" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G164" t="s">
         <v>89</v>
@@ -7654,18 +7591,18 @@
       <c r="I164" t="s">
         <v>58</v>
       </c>
+      <c r="J164">
+        <v>19</v>
+      </c>
       <c r="K164">
-        <v>19</v>
-      </c>
-      <c r="L164">
         <v>1</v>
       </c>
-      <c r="M164" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L164" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C164),E164)</f>
         <v>Falcon 90 Proto</v>
       </c>
     </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>163</v>
       </c>
@@ -7676,13 +7613,13 @@
         <v>201</v>
       </c>
       <c r="E165" t="s">
+        <v>341</v>
+      </c>
+      <c r="F165" t="s">
         <v>342</v>
       </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>343</v>
-      </c>
-      <c r="G165" t="s">
-        <v>344</v>
       </c>
       <c r="H165">
         <v>2007</v>
@@ -7690,18 +7627,18 @@
       <c r="I165" t="s">
         <v>227</v>
       </c>
+      <c r="J165">
+        <v>24</v>
+      </c>
       <c r="K165">
-        <v>24</v>
-      </c>
-      <c r="L165">
         <v>8</v>
       </c>
-      <c r="M165" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L165" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C165),E165)</f>
         <v>Falcon Formula TT</v>
       </c>
     </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>164</v>
       </c>
@@ -7712,13 +7649,13 @@
         <v>201</v>
       </c>
       <c r="E166" t="s">
+        <v>344</v>
+      </c>
+      <c r="F166" t="s">
         <v>345</v>
       </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>346</v>
-      </c>
-      <c r="G166" t="s">
-        <v>347</v>
       </c>
       <c r="H166">
         <v>2007</v>
@@ -7726,18 +7663,18 @@
       <c r="I166" t="s">
         <v>22</v>
       </c>
+      <c r="J166">
+        <v>25</v>
+      </c>
       <c r="K166">
-        <v>25</v>
-      </c>
-      <c r="L166">
         <v>1</v>
       </c>
-      <c r="M166" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L166" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C166),E166)</f>
         <v>Falcon prototype</v>
       </c>
     </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>165</v>
       </c>
@@ -7748,10 +7685,10 @@
         <v>201</v>
       </c>
       <c r="E167" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F167" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G167" t="s">
         <v>42</v>
@@ -7762,18 +7699,18 @@
       <c r="I167" t="s">
         <v>58</v>
       </c>
+      <c r="J167">
+        <v>71</v>
+      </c>
       <c r="K167">
-        <v>71</v>
-      </c>
-      <c r="L167">
         <v>3</v>
       </c>
-      <c r="M167" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L167" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C167),E167)</f>
         <v>Falcon SL 105</v>
       </c>
     </row>
-    <row r="168" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>166</v>
       </c>
@@ -7784,13 +7721,13 @@
         <v>201</v>
       </c>
       <c r="E168" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F168" t="s">
+        <v>337</v>
+      </c>
+      <c r="G168" t="s">
         <v>338</v>
-      </c>
-      <c r="G168" t="s">
-        <v>339</v>
       </c>
       <c r="H168">
         <v>2007</v>
@@ -7798,18 +7735,18 @@
       <c r="I168" t="s">
         <v>67</v>
       </c>
+      <c r="J168">
+        <v>41</v>
+      </c>
       <c r="K168">
-        <v>41</v>
-      </c>
-      <c r="L168">
         <v>3</v>
       </c>
-      <c r="M168" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L168" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C168),E168)</f>
         <v>Falcon SL 145</v>
       </c>
     </row>
-    <row r="169" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>167</v>
       </c>
@@ -7820,10 +7757,10 @@
         <v>201</v>
       </c>
       <c r="E169" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F169" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G169" t="s">
         <v>89</v>
@@ -7834,18 +7771,18 @@
       <c r="I169" t="s">
         <v>58</v>
       </c>
+      <c r="J169">
+        <v>140</v>
+      </c>
       <c r="K169">
-        <v>140</v>
-      </c>
-      <c r="L169">
         <v>6</v>
       </c>
-      <c r="M169" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L169" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C169),E169)</f>
         <v>Falcon SL90</v>
       </c>
     </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>168</v>
       </c>
@@ -7856,10 +7793,10 @@
         <v>201</v>
       </c>
       <c r="E170" t="s">
+        <v>350</v>
+      </c>
+      <c r="F170" t="s">
         <v>351</v>
-      </c>
-      <c r="F170" t="s">
-        <v>352</v>
       </c>
       <c r="G170" t="s">
         <v>79</v>
@@ -7870,18 +7807,18 @@
       <c r="I170" t="s">
         <v>58</v>
       </c>
+      <c r="J170">
+        <v>45</v>
+      </c>
       <c r="K170">
-        <v>45</v>
-      </c>
-      <c r="L170">
         <v>2</v>
       </c>
-      <c r="M170" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L170" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C170),E170)</f>
         <v>Falcon Slalom 105</v>
       </c>
     </row>
-    <row r="171" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>169</v>
       </c>
@@ -7892,13 +7829,13 @@
         <v>201</v>
       </c>
       <c r="E171" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F171" t="s">
         <v>105</v>
       </c>
       <c r="G171" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H171">
         <v>2007</v>
@@ -7906,15 +7843,15 @@
       <c r="I171" t="s">
         <v>43</v>
       </c>
-      <c r="K171">
+      <c r="J171">
         <v>2</v>
       </c>
-      <c r="M171" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L171" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C171),E171)</f>
         <v>Falcon Speed</v>
       </c>
     </row>
-    <row r="172" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>170</v>
       </c>
@@ -7925,13 +7862,13 @@
         <v>201</v>
       </c>
       <c r="E172" t="s">
+        <v>354</v>
+      </c>
+      <c r="F172" t="s">
         <v>355</v>
       </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>356</v>
-      </c>
-      <c r="G172" t="s">
-        <v>357</v>
       </c>
       <c r="H172">
         <v>2007</v>
@@ -7939,18 +7876,18 @@
       <c r="I172" t="s">
         <v>61</v>
       </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
       <c r="K172">
         <v>1</v>
       </c>
-      <c r="L172">
-        <v>1</v>
-      </c>
-      <c r="M172" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L172" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C172),E172)</f>
         <v>Freemove</v>
       </c>
     </row>
-    <row r="173" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>171</v>
       </c>
@@ -7961,10 +7898,10 @@
         <v>201</v>
       </c>
       <c r="E173" t="s">
+        <v>357</v>
+      </c>
+      <c r="F173" t="s">
         <v>358</v>
-      </c>
-      <c r="F173" t="s">
-        <v>359</v>
       </c>
       <c r="G173" t="s">
         <v>175</v>
@@ -7975,18 +7912,18 @@
       <c r="I173" t="s">
         <v>26</v>
       </c>
+      <c r="J173">
+        <v>5</v>
+      </c>
       <c r="K173">
-        <v>5</v>
-      </c>
-      <c r="L173">
         <v>2</v>
       </c>
-      <c r="M173" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L173" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C173),E173)</f>
         <v>Freewave</v>
       </c>
     </row>
-    <row r="174" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>172</v>
       </c>
@@ -7997,10 +7934,10 @@
         <v>201</v>
       </c>
       <c r="E174" t="s">
+        <v>359</v>
+      </c>
+      <c r="F174" t="s">
         <v>360</v>
-      </c>
-      <c r="F174" t="s">
-        <v>361</v>
       </c>
       <c r="G174" t="s">
         <v>232</v>
@@ -8011,18 +7948,18 @@
       <c r="I174" t="s">
         <v>26</v>
       </c>
+      <c r="J174">
+        <v>20</v>
+      </c>
       <c r="K174">
-        <v>20</v>
-      </c>
-      <c r="L174">
-        <v>10</v>
-      </c>
-      <c r="M174" s="1" t="str">
-        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L174" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C174),E174)</f>
         <v>Freewave 104</v>
       </c>
     </row>
-    <row r="175" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>173</v>
       </c>
@@ -8033,13 +7970,13 @@
         <v>201</v>
       </c>
       <c r="E175" t="s">
+        <v>361</v>
+      </c>
+      <c r="F175" t="s">
         <v>362</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>363</v>
-      </c>
-      <c r="G175" t="s">
-        <v>364</v>
       </c>
       <c r="H175">
         <v>2007</v>
@@ -8047,18 +7984,18 @@
       <c r="I175" t="s">
         <v>26</v>
       </c>
+      <c r="J175">
+        <v>63</v>
+      </c>
       <c r="K175">
-        <v>63</v>
-      </c>
-      <c r="L175">
         <v>5</v>
       </c>
-      <c r="M175" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L175" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C175),E175)</f>
         <v>Freewave 86</v>
       </c>
     </row>
-    <row r="176" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>174</v>
       </c>
@@ -8069,13 +8006,13 @@
         <v>201</v>
       </c>
       <c r="E176" t="s">
+        <v>364</v>
+      </c>
+      <c r="F176" t="s">
         <v>365</v>
       </c>
-      <c r="F176" t="s">
-        <v>366</v>
-      </c>
       <c r="G176" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H176">
         <v>2007</v>
@@ -8083,18 +8020,18 @@
       <c r="I176" t="s">
         <v>26</v>
       </c>
+      <c r="J176">
+        <v>103</v>
+      </c>
       <c r="K176">
-        <v>103</v>
-      </c>
-      <c r="L176">
-        <v>10</v>
-      </c>
-      <c r="M176" s="1" t="str">
-        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L176" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C176),E176)</f>
         <v>Freewave 95</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>175</v>
       </c>
@@ -8105,13 +8042,13 @@
         <v>201</v>
       </c>
       <c r="E177" t="s">
+        <v>366</v>
+      </c>
+      <c r="F177" t="s">
         <v>367</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>368</v>
-      </c>
-      <c r="G177" t="s">
-        <v>369</v>
       </c>
       <c r="H177">
         <v>2007</v>
@@ -8119,18 +8056,18 @@
       <c r="I177" t="s">
         <v>58</v>
       </c>
+      <c r="J177">
+        <v>84</v>
+      </c>
       <c r="K177">
-        <v>84</v>
-      </c>
-      <c r="L177">
         <v>11</v>
       </c>
-      <c r="M177" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L177" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C177),E177)</f>
         <v>Hawk 108</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>176</v>
       </c>
@@ -8141,13 +8078,13 @@
         <v>201</v>
       </c>
       <c r="E178" t="s">
+        <v>369</v>
+      </c>
+      <c r="F178" t="s">
         <v>370</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>371</v>
-      </c>
-      <c r="G178" t="s">
-        <v>372</v>
       </c>
       <c r="H178">
         <v>2007</v>
@@ -8155,18 +8092,18 @@
       <c r="I178" t="s">
         <v>58</v>
       </c>
+      <c r="J178">
+        <v>6</v>
+      </c>
       <c r="K178">
-        <v>6</v>
-      </c>
-      <c r="L178">
         <v>5</v>
       </c>
-      <c r="M178" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L178" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C178),E178)</f>
         <v>Hawk 123</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>177</v>
       </c>
@@ -8177,13 +8114,13 @@
         <v>201</v>
       </c>
       <c r="E179" t="s">
+        <v>372</v>
+      </c>
+      <c r="F179" t="s">
         <v>373</v>
       </c>
-      <c r="F179" t="s">
-        <v>374</v>
-      </c>
       <c r="G179" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H179">
         <v>2007</v>
@@ -8191,18 +8128,18 @@
       <c r="I179" t="s">
         <v>22</v>
       </c>
+      <c r="J179">
+        <v>25</v>
+      </c>
       <c r="K179">
-        <v>25</v>
-      </c>
-      <c r="L179">
         <v>6</v>
       </c>
-      <c r="M179" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L179" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C179),E179)</f>
         <v>Shark</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>178</v>
       </c>
@@ -8213,10 +8150,10 @@
         <v>201</v>
       </c>
       <c r="E180" t="s">
+        <v>374</v>
+      </c>
+      <c r="F180" t="s">
         <v>375</v>
-      </c>
-      <c r="F180" t="s">
-        <v>376</v>
       </c>
       <c r="G180" t="s">
         <v>35</v>
@@ -8227,18 +8164,18 @@
       <c r="I180" t="s">
         <v>22</v>
       </c>
+      <c r="J180">
+        <v>84</v>
+      </c>
       <c r="K180">
-        <v>84</v>
-      </c>
-      <c r="L180">
         <v>9</v>
       </c>
-      <c r="M180" s="1" t="str">
-        <f t="shared" si="0"/>
+      <c r="L180" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C180),E180)</f>
         <v>Shark 130 Ltd</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>179</v>
       </c>
@@ -8249,13 +8186,13 @@
         <v>201</v>
       </c>
       <c r="E181" t="s">
+        <v>376</v>
+      </c>
+      <c r="F181" t="s">
         <v>377</v>
       </c>
-      <c r="F181" t="s">
-        <v>378</v>
-      </c>
       <c r="G181" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H181">
         <v>2007</v>
@@ -8263,20 +8200,479 @@
       <c r="I181" t="s">
         <v>22</v>
       </c>
+      <c r="J181">
+        <v>24</v>
+      </c>
       <c r="K181">
+        <v>4</v>
+      </c>
+      <c r="L181" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C181),E181)</f>
+        <v>Shark HRS 145 L</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A182" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="B182">
+        <v>180</v>
+      </c>
+      <c r="C182">
+        <v>14297</v>
+      </c>
+      <c r="D182" t="s">
+        <v>208</v>
+      </c>
+      <c r="E182" t="s">
+        <v>378</v>
+      </c>
+      <c r="F182" t="s">
+        <v>379</v>
+      </c>
+      <c r="G182" t="s">
+        <v>380</v>
+      </c>
+      <c r="H182">
+        <v>2004</v>
+      </c>
+      <c r="I182" t="s">
+        <v>22</v>
+      </c>
+      <c r="J182">
+        <v>4</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C182),E182)</f>
+        <v>Attitude Inspiro 79</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B183">
+        <v>181</v>
+      </c>
+      <c r="C183">
+        <v>661</v>
+      </c>
+      <c r="D183" t="s">
+        <v>208</v>
+      </c>
+      <c r="E183" t="s">
+        <v>381</v>
+      </c>
+      <c r="F183" t="s">
+        <v>408</v>
+      </c>
+      <c r="G183" t="s">
+        <v>409</v>
+      </c>
+      <c r="H183">
+        <v>2004</v>
+      </c>
+      <c r="I183" t="s">
+        <v>67</v>
+      </c>
+      <c r="J183">
+        <v>3</v>
+      </c>
+      <c r="L183" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C183),E183)</f>
+        <v>Attitude Inspiro 87</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B184">
+        <v>182</v>
+      </c>
+      <c r="C184">
+        <v>1218</v>
+      </c>
+      <c r="D184" t="s">
+        <v>208</v>
+      </c>
+      <c r="E184" t="s">
+        <v>382</v>
+      </c>
+      <c r="F184" t="s">
+        <v>383</v>
+      </c>
+      <c r="G184" t="s">
+        <v>384</v>
+      </c>
+      <c r="H184">
+        <v>2004</v>
+      </c>
+      <c r="I184" t="s">
+        <v>227</v>
+      </c>
+      <c r="J184">
+        <v>47</v>
+      </c>
+      <c r="K184">
+        <v>4</v>
+      </c>
+      <c r="L184" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C184),E184)</f>
+        <v>Formula 98 N.T.</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B185">
+        <v>183</v>
+      </c>
+      <c r="C185">
+        <v>335</v>
+      </c>
+      <c r="D185" t="s">
+        <v>208</v>
+      </c>
+      <c r="E185" t="s">
+        <v>385</v>
+      </c>
+      <c r="F185" t="s">
+        <v>386</v>
+      </c>
+      <c r="G185" t="s">
+        <v>387</v>
+      </c>
+      <c r="H185">
+        <v>2004</v>
+      </c>
+      <c r="I185" t="s">
+        <v>61</v>
+      </c>
+      <c r="J185">
+        <v>4</v>
+      </c>
+      <c r="L185" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C185),E185)</f>
+        <v>GT Special 54</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B186">
+        <v>184</v>
+      </c>
+      <c r="C186">
+        <v>679</v>
+      </c>
+      <c r="D186" t="s">
+        <v>208</v>
+      </c>
+      <c r="E186" t="s">
+        <v>388</v>
+      </c>
+      <c r="F186" t="s">
+        <v>389</v>
+      </c>
+      <c r="G186" t="s">
+        <v>46</v>
+      </c>
+      <c r="H186">
+        <v>2004</v>
+      </c>
+      <c r="I186" t="s">
+        <v>22</v>
+      </c>
+      <c r="J186">
+        <v>36</v>
+      </c>
+      <c r="K186">
+        <v>8</v>
+      </c>
+      <c r="L186" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C186),E186)</f>
+        <v>GT Special 73</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B187">
+        <v>185</v>
+      </c>
+      <c r="C187">
+        <v>3459</v>
+      </c>
+      <c r="D187" t="s">
+        <v>208</v>
+      </c>
+      <c r="E187" t="s">
+        <v>390</v>
+      </c>
+      <c r="F187" t="s">
+        <v>391</v>
+      </c>
+      <c r="G187" t="s">
+        <v>384</v>
+      </c>
+      <c r="H187">
+        <v>2004</v>
+      </c>
+      <c r="I187" t="s">
+        <v>67</v>
+      </c>
+      <c r="J187">
+        <v>10</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C187),E187)</f>
+        <v>GT Special 86</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B188">
+        <v>186</v>
+      </c>
+      <c r="C188">
+        <v>3475</v>
+      </c>
+      <c r="D188" t="s">
+        <v>208</v>
+      </c>
+      <c r="E188" t="s">
+        <v>392</v>
+      </c>
+      <c r="F188" t="s">
+        <v>393</v>
+      </c>
+      <c r="G188" t="s">
+        <v>394</v>
+      </c>
+      <c r="H188">
+        <v>2004</v>
+      </c>
+      <c r="I188" t="s">
+        <v>26</v>
+      </c>
+      <c r="J188">
+        <v>2</v>
+      </c>
+      <c r="L188" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C188),E188)</f>
+        <v>Kauli Pro 81</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B189">
+        <v>187</v>
+      </c>
+      <c r="C189">
+        <v>826</v>
+      </c>
+      <c r="D189" t="s">
+        <v>208</v>
+      </c>
+      <c r="E189" t="s">
+        <v>395</v>
+      </c>
+      <c r="F189" t="s">
+        <v>396</v>
+      </c>
+      <c r="G189" t="s">
+        <v>232</v>
+      </c>
+      <c r="H189">
+        <v>2004</v>
+      </c>
+      <c r="I189" t="s">
+        <v>26</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>3</v>
+      </c>
+      <c r="L189" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C189),E189)</f>
+        <v>Maxx Ride 104</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B190">
+        <v>188</v>
+      </c>
+      <c r="C190">
+        <v>2436</v>
+      </c>
+      <c r="D190" t="s">
+        <v>208</v>
+      </c>
+      <c r="E190" t="s">
+        <v>397</v>
+      </c>
+      <c r="F190" t="s">
+        <v>398</v>
+      </c>
+      <c r="G190" t="s">
+        <v>52</v>
+      </c>
+      <c r="H190">
+        <v>2004</v>
+      </c>
+      <c r="I190" t="s">
+        <v>26</v>
+      </c>
+      <c r="J190">
+        <v>2</v>
+      </c>
+      <c r="L190" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C190),E190)</f>
+        <v>Maxx Ride 92</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B191">
+        <v>189</v>
+      </c>
+      <c r="C191">
+        <v>3745</v>
+      </c>
+      <c r="D191" t="s">
+        <v>208</v>
+      </c>
+      <c r="E191" t="s">
+        <v>399</v>
+      </c>
+      <c r="F191" t="s">
+        <v>400</v>
+      </c>
+      <c r="G191" t="s">
+        <v>322</v>
+      </c>
+      <c r="H191">
+        <v>2004</v>
+      </c>
+      <c r="I191" t="s">
+        <v>26</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C191),E191)</f>
+        <v>Mx 57</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B192">
+        <v>190</v>
+      </c>
+      <c r="C192">
+        <v>2111</v>
+      </c>
+      <c r="D192" t="s">
+        <v>208</v>
+      </c>
+      <c r="E192" t="s">
+        <v>401</v>
+      </c>
+      <c r="F192" t="s">
+        <v>402</v>
+      </c>
+      <c r="G192" t="s">
+        <v>403</v>
+      </c>
+      <c r="H192">
+        <v>2004</v>
+      </c>
+      <c r="I192" t="s">
+        <v>58</v>
+      </c>
+      <c r="J192">
         <v>24</v>
       </c>
-      <c r="L181">
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C192),E192)</f>
+        <v>Type F 64</v>
+      </c>
+    </row>
+    <row r="193" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B193">
+        <v>191</v>
+      </c>
+      <c r="C193">
+        <v>1679</v>
+      </c>
+      <c r="D193" t="s">
+        <v>208</v>
+      </c>
+      <c r="E193" t="s">
+        <v>404</v>
+      </c>
+      <c r="F193" t="s">
+        <v>405</v>
+      </c>
+      <c r="G193" t="s">
+        <v>335</v>
+      </c>
+      <c r="H193">
+        <v>2004</v>
+      </c>
+      <c r="I193" t="s">
+        <v>22</v>
+      </c>
+      <c r="J193">
+        <v>32</v>
+      </c>
+      <c r="K193">
         <v>4</v>
       </c>
-      <c r="M181" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Shark HRS 145 L</v>
+      <c r="L193" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C193),E193)</f>
+        <v>Type F 75</v>
+      </c>
+    </row>
+    <row r="194" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B194">
+        <v>192</v>
+      </c>
+      <c r="C194">
+        <v>1952</v>
+      </c>
+      <c r="D194" t="s">
+        <v>208</v>
+      </c>
+      <c r="E194" t="s">
+        <v>406</v>
+      </c>
+      <c r="F194" t="s">
+        <v>407</v>
+      </c>
+      <c r="G194" t="s">
+        <v>338</v>
+      </c>
+      <c r="H194">
+        <v>2004</v>
+      </c>
+      <c r="I194" t="s">
+        <v>67</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>1</v>
+      </c>
+      <c r="L194" s="1" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT($F$1,C194),E194)</f>
+        <v>Type F 85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M181">
+  <autoFilter ref="A2:L2" xr:uid="{CA576202-A1A0-4430-9DEF-EFCA8AEA998F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L194">
       <sortCondition ref="B2"/>
     </sortState>
   </autoFilter>
